--- a/database/event/2109/event_2109_evp_summary.xlsx
+++ b/database/event/2109/event_2109_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.5531</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2926</v>
+        <v>2.2326</v>
       </c>
       <c r="E2" t="n">
         <v>6.7182</v>
@@ -548,7 +548,7 @@
         <v>1.0809</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4675</v>
+        <v>1.4189</v>
       </c>
       <c r="E3" t="n">
         <v>4.6757</v>
@@ -594,7 +594,7 @@
         <v>1.0571</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4259</v>
+        <v>1.3779</v>
       </c>
       <c r="E4" t="n">
         <v>4.5727</v>
@@ -630,231 +630,231 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.8924</v>
+        <v>4.0861</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8998</v>
+        <v>0.9446</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1511</v>
+        <v>1.184</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8924</v>
+        <v>4.0861</v>
       </c>
       <c r="F5" t="n">
-        <v>2.865</v>
+        <v>2.9596</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0274</v>
+        <v>1.1265</v>
       </c>
       <c r="H5" t="n">
-        <v>2.865</v>
+        <v>2.9596</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3222</v>
+        <v>2.3988</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0274</v>
+        <v>1.1265</v>
       </c>
       <c r="K5" t="n">
-        <v>153</v>
+        <v>50</v>
       </c>
       <c r="L5" t="n">
+        <v>84</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.5253</v>
+      </c>
+      <c r="N5" t="n">
         <v>134</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.3496</v>
-      </c>
-      <c r="N5" t="n">
-        <v>287</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4972</v>
+        <v>3.8924</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8085</v>
+        <v>0.8998</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9913999999999999</v>
+        <v>1.1068</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4972</v>
+        <v>3.8924</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3707</v>
+        <v>2.865</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1265</v>
+        <v>1.0274</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3707</v>
+        <v>2.865</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9215</v>
+        <v>2.3222</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1265</v>
+        <v>1.0274</v>
       </c>
       <c r="K6" t="n">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="L6" t="n">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="M6" t="n">
-        <v>3.048</v>
+        <v>3.3496</v>
       </c>
       <c r="N6" t="n">
-        <v>134</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>znajder</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5802</v>
+        <v>3.4266</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5965</v>
+        <v>0.7922</v>
       </c>
       <c r="D7" t="n">
-        <v>0.621</v>
+        <v>0.9212</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5802</v>
+        <v>3.4266</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6083</v>
+        <v>3.7496</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9719</v>
+        <v>-0.323</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6083</v>
+        <v>3.7496</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3036</v>
+        <v>3.0392</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9719</v>
+        <v>-0.323</v>
       </c>
       <c r="K7" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L7" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2755</v>
+        <v>2.7162</v>
       </c>
       <c r="N7" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5543</v>
+        <v>2.862</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5905</v>
+        <v>0.6616</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6105</v>
+        <v>0.6963</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5543</v>
+        <v>2.862</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6538</v>
+        <v>1.8901</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0995</v>
+        <v>0.9719</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6538</v>
+        <v>1.8901</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9615</v>
+        <v>1.532</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0995</v>
+        <v>0.9719</v>
       </c>
       <c r="K8" t="n">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="M8" t="n">
-        <v>1.862</v>
+        <v>2.5039</v>
       </c>
       <c r="N8" t="n">
-        <v>247</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>znajder</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5336</v>
+        <v>2.8494</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5857</v>
+        <v>0.6587</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6022</v>
+        <v>0.6913</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5336</v>
+        <v>2.8494</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8566</v>
+        <v>3.9489</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.323</v>
+        <v>-1.0995</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8566</v>
+        <v>3.9489</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3153</v>
+        <v>3.2007</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.323</v>
+        <v>-1.0995</v>
       </c>
       <c r="K9" t="n">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="L9" t="n">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9923</v>
+        <v>2.1012</v>
       </c>
       <c r="N9" t="n">
-        <v>126</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3543</v>
+        <v>2.6523</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5443</v>
+        <v>0.6132</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.6128</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3543</v>
+        <v>2.6523</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.863</v>
       </c>
       <c r="G10" t="n">
         <v>1.7893</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.863</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4579</v>
+        <v>0.6995</v>
       </c>
       <c r="J10" t="n">
         <v>1.7893</v>
@@ -897,7 +897,7 @@
         <v>84</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2472</v>
+        <v>2.4888</v>
       </c>
       <c r="N10" t="n">
         <v>134</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.227</v>
+        <v>2.2298</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5148</v>
+        <v>0.5155</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4783</v>
+        <v>0.4444</v>
       </c>
       <c r="E11" t="n">
-        <v>2.227</v>
+        <v>2.2298</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5421</v>
+        <v>1.5449</v>
       </c>
       <c r="G11" t="n">
         <v>0.6849</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5421</v>
+        <v>1.5449</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2499</v>
+        <v>1.2522</v>
       </c>
       <c r="J11" t="n">
         <v>0.6849</v>
@@ -943,7 +943,7 @@
         <v>79</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9348</v>
+        <v>1.9371</v>
       </c>
       <c r="N11" t="n">
         <v>126</v>
@@ -962,7 +962,7 @@
         <v>0.4473</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3603</v>
+        <v>0.327</v>
       </c>
       <c r="E12" t="n">
         <v>1.935</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4469</v>
+        <v>1.6377</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3345</v>
+        <v>0.3786</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1632</v>
+        <v>0.2085</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4469</v>
+        <v>1.6377</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2173</v>
+        <v>1.4081</v>
       </c>
       <c r="G13" t="n">
         <v>0.2296</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2173</v>
+        <v>1.4081</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9867</v>
+        <v>1.1413</v>
       </c>
       <c r="J13" t="n">
         <v>0.2296</v>
@@ -1035,7 +1035,7 @@
         <v>139</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2163</v>
+        <v>1.3709</v>
       </c>
       <c r="N13" t="n">
         <v>247</v>
@@ -1044,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>disco doplan</t>
+          <t>Friis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1921</v>
+        <v>1.3519</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2756</v>
+        <v>0.3125</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0602</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1921</v>
+        <v>1.3519</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1921</v>
+        <v>1.3519</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1921</v>
+        <v>1.3519</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1921</v>
+        <v>1.3519</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1921</v>
+        <v>1.3519</v>
       </c>
       <c r="N14" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>pronax</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1823</v>
+        <v>1.289</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2733</v>
+        <v>0.298</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0563</v>
+        <v>0.0696</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1823</v>
+        <v>1.289</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4399</v>
+        <v>2.0902</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2576</v>
+        <v>-0.8012</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4399</v>
+        <v>2.0902</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1671</v>
+        <v>1.6942</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2576</v>
+        <v>-0.8012</v>
       </c>
       <c r="K15" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L15" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9095</v>
+        <v>0.8929999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Friis</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1507</v>
+        <v>1.2221</v>
       </c>
       <c r="C16" t="n">
-        <v>0.266</v>
+        <v>0.2825</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0435</v>
+        <v>0.043</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1507</v>
+        <v>1.2221</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1507</v>
+        <v>1.4797</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.2576</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1507</v>
+        <v>1.4797</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1507</v>
+        <v>1.1993</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.2576</v>
       </c>
       <c r="K16" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1507</v>
+        <v>0.9417</v>
       </c>
       <c r="N16" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pronax</t>
+          <t>disco doplan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0859</v>
+        <v>1.1921</v>
       </c>
       <c r="C17" t="n">
-        <v>0.251</v>
+        <v>0.2756</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0173</v>
+        <v>0.031</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0859</v>
+        <v>1.1921</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8871</v>
+        <v>1.1921</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8012</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8871</v>
+        <v>1.1921</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5295</v>
+        <v>1.1921</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8012</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="L17" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7283000000000001</v>
+        <v>1.1921</v>
       </c>
       <c r="N17" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18">
@@ -1238,7 +1238,7 @@
         <v>0.2162</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0435</v>
+        <v>-0.0712</v>
       </c>
       <c r="E18" t="n">
         <v>0.9354</v>
@@ -1284,7 +1284,7 @@
         <v>0.1947</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.1084</v>
       </c>
       <c r="E19" t="n">
         <v>0.8421999999999999</v>
@@ -1330,7 +1330,7 @@
         <v>0.1312</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.192</v>
+        <v>-0.2177</v>
       </c>
       <c r="E20" t="n">
         <v>0.5677</v>
@@ -1376,7 +1376,7 @@
         <v>0.1213</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2094</v>
+        <v>-0.2349</v>
       </c>
       <c r="E21" t="n">
         <v>0.5246</v>
@@ -1422,7 +1422,7 @@
         <v>0.1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2466</v>
+        <v>-0.2715</v>
       </c>
       <c r="E22" t="n">
         <v>0.4327</v>
@@ -1458,369 +1458,369 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.2076</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0154</v>
+        <v>0.048</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3945</v>
+        <v>-0.3612</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.2076</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06660000000000001</v>
+        <v>1.2076</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.06660000000000001</v>
+        <v>1.2076</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.9788</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K23" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M23" t="n">
-        <v>0.06660000000000001</v>
+        <v>-0.0212</v>
       </c>
       <c r="N23" t="n">
-        <v>78</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.133</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0307</v>
+        <v>0.0154</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4751</v>
+        <v>-0.4174</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.133</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0776</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0554</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0776</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0629</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0554</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="L24" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1183</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>126</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1911</v>
+        <v>-0.133</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0442</v>
+        <v>-0.0307</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4986</v>
+        <v>-0.4969</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1911</v>
+        <v>-0.133</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2996</v>
+        <v>-0.0776</v>
       </c>
       <c r="G25" t="n">
-        <v>2.1085</v>
+        <v>-0.0554</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.2996</v>
+        <v>-0.0776</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.8639</v>
+        <v>-0.0629</v>
       </c>
       <c r="J25" t="n">
-        <v>2.1085</v>
+        <v>-0.0554</v>
       </c>
       <c r="K25" t="n">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="L25" t="n">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2445999999999999</v>
+        <v>-0.1183</v>
       </c>
       <c r="N25" t="n">
-        <v>287</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2315</v>
+        <v>-0.1333</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0535</v>
+        <v>-0.0308</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5149</v>
+        <v>-0.497</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2315</v>
+        <v>-0.1333</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7685</v>
+        <v>-0.1333</v>
       </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7685</v>
+        <v>-0.1333</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6229</v>
+        <v>-0.1333</v>
       </c>
       <c r="J26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="L26" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3771</v>
+        <v>-0.1333</v>
       </c>
       <c r="N26" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2726</v>
+        <v>-0.1911</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.063</v>
+        <v>-0.0442</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5315</v>
+        <v>-0.52</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2726</v>
+        <v>-0.1911</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2726</v>
+        <v>-2.2996</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.1085</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2726</v>
+        <v>-2.2996</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2726</v>
+        <v>-1.8639</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2.1085</v>
       </c>
       <c r="K27" t="n">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2726</v>
+        <v>0.2445999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>78</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>pauf</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2744</v>
+        <v>-0.2449</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0634</v>
+        <v>-0.0566</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5322</v>
+        <v>-0.5415</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2744</v>
+        <v>-0.2449</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2744</v>
+        <v>0.1659</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.4108</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2744</v>
+        <v>0.1659</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2744</v>
+        <v>0.1345</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.4108</v>
       </c>
       <c r="K28" t="n">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2744</v>
+        <v>-0.2763</v>
       </c>
       <c r="N28" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2797</v>
+        <v>-0.2726</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.063</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5344</v>
+        <v>-0.5525</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2797</v>
+        <v>-0.2726</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2797</v>
+        <v>-0.2726</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2797</v>
+        <v>-0.2726</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2797</v>
+        <v>-0.2726</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2797</v>
+        <v>-0.2726</v>
       </c>
       <c r="N29" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pauf</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3453</v>
+        <v>-0.2797</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0798</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5609</v>
+        <v>-0.5553</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3453</v>
+        <v>-0.2797</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0655</v>
+        <v>-0.2797</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4108</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0655</v>
+        <v>-0.2797</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0531</v>
+        <v>-0.2797</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4108</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="L30" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3577</v>
+        <v>-0.2797</v>
       </c>
       <c r="N30" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
@@ -1836,7 +1836,7 @@
         <v>-0.107</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.6284</v>
       </c>
       <c r="E31" t="n">
         <v>-0.463</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1255</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6407</v>
+        <v>-0.6602</v>
       </c>
       <c r="E32" t="n">
         <v>-0.5429</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1256</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6408</v>
+        <v>-0.6604</v>
       </c>
       <c r="E33" t="n">
         <v>-0.5433</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1438</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6727</v>
+        <v>-0.6918</v>
       </c>
       <c r="E34" t="n">
         <v>-0.6221</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2316</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.8431</v>
       </c>
       <c r="E35" t="n">
         <v>-1.0019</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>naSu</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0906</v>
+        <v>-1.0468</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2521</v>
+        <v>-0.242</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8619</v>
+        <v>-0.861</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0906</v>
+        <v>-1.0468</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0906</v>
+        <v>-0.5121</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.5347</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0906</v>
+        <v>-0.5121</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0906</v>
+        <v>-0.4151</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.5347</v>
       </c>
       <c r="K36" t="n">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0906</v>
+        <v>-0.9498</v>
       </c>
       <c r="N36" t="n">
-        <v>75</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>naSu</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.151</v>
+        <v>-1.0906</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2661</v>
+        <v>-0.2521</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8863</v>
+        <v>-0.8784</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.151</v>
+        <v>-1.0906</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6163</v>
+        <v>-1.0906</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5347</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6163</v>
+        <v>-1.0906</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4995</v>
+        <v>-1.0906</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5347</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="L37" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0342</v>
+        <v>-1.0906</v>
       </c>
       <c r="N37" t="n">
-        <v>247</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38">
@@ -2158,7 +2158,7 @@
         <v>-0.2706</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8942</v>
+        <v>-0.9102</v>
       </c>
       <c r="E38" t="n">
         <v>-1.1704</v>
@@ -2204,7 +2204,7 @@
         <v>-0.3004</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9463</v>
+        <v>-0.9616</v>
       </c>
       <c r="E39" t="n">
         <v>-1.2993</v>
@@ -2250,7 +2250,7 @@
         <v>-0.3194</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9794</v>
+        <v>-0.9943</v>
       </c>
       <c r="E40" t="n">
         <v>-1.3814</v>
@@ -2296,7 +2296,7 @@
         <v>-0.3891</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1013</v>
+        <v>-1.1145</v>
       </c>
       <c r="E41" t="n">
         <v>-1.6832</v>

--- a/database/event/2109/event_2109_evp_summary.xlsx
+++ b/database/event/2109/event_2109_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7182</v>
+        <v>6.401</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5531</v>
+        <v>1.4798</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2326</v>
+        <v>2.2517</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7182</v>
+        <v>6.401</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3649</v>
+        <v>3.9586</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3533</v>
+        <v>2.4424</v>
       </c>
       <c r="H2" t="n">
-        <v>5.0006</v>
+        <v>8.4613</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0531</v>
+        <v>4.3995</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3533</v>
+        <v>2.4424</v>
       </c>
       <c r="K2" t="n">
         <v>153</v>
@@ -529,7 +529,7 @@
         <v>134</v>
       </c>
       <c r="M2" t="n">
-        <v>6.4064</v>
+        <v>6.8419</v>
       </c>
       <c r="N2" t="n">
         <v>287</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.6757</v>
+        <v>4.9932</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0809</v>
+        <v>1.1543</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4189</v>
+        <v>1.6162</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6757</v>
+        <v>4.9932</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3658</v>
+        <v>2.3308</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3099</v>
+        <v>2.6624</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3658</v>
+        <v>2.7258</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9175</v>
+        <v>1.4173</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3099</v>
+        <v>2.6624</v>
       </c>
       <c r="K3" t="n">
         <v>153</v>
@@ -575,7 +575,7 @@
         <v>134</v>
       </c>
       <c r="M3" t="n">
-        <v>4.227399999999999</v>
+        <v>4.0797</v>
       </c>
       <c r="N3" t="n">
         <v>287</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5727</v>
+        <v>4.942</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0571</v>
+        <v>1.1425</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3779</v>
+        <v>1.5931</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5727</v>
+        <v>4.942</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4888</v>
+        <v>2.705</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0839</v>
+        <v>2.237</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4888</v>
+        <v>4.0444</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2067</v>
+        <v>2.1029</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0839</v>
+        <v>2.237</v>
       </c>
       <c r="K4" t="n">
         <v>153</v>
@@ -621,7 +621,7 @@
         <v>134</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2906</v>
+        <v>4.3399</v>
       </c>
       <c r="N4" t="n">
         <v>287</v>
@@ -630,311 +630,311 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0861</v>
+        <v>4.1623</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9446</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.184</v>
+        <v>1.2411</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0861</v>
+        <v>4.1623</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9596</v>
+        <v>2.9747</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1265</v>
+        <v>1.1876</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9596</v>
+        <v>4.9947</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3988</v>
+        <v>2.597</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1265</v>
+        <v>1.1876</v>
       </c>
       <c r="K5" t="n">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="L5" t="n">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5253</v>
+        <v>3.7846</v>
       </c>
       <c r="N5" t="n">
-        <v>134</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8924</v>
+        <v>3.742</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8998</v>
+        <v>0.8651</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1068</v>
+        <v>1.0513</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8924</v>
+        <v>3.742</v>
       </c>
       <c r="F6" t="n">
-        <v>2.865</v>
+        <v>2.8146</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0274</v>
+        <v>0.9274</v>
       </c>
       <c r="H6" t="n">
-        <v>2.865</v>
+        <v>4.4306</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3222</v>
+        <v>2.3037</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0274</v>
+        <v>0.9274</v>
       </c>
       <c r="K6" t="n">
-        <v>153</v>
+        <v>50</v>
       </c>
       <c r="L6" t="n">
+        <v>84</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.2311</v>
+      </c>
+      <c r="N6" t="n">
         <v>134</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.3496</v>
-      </c>
-      <c r="N6" t="n">
-        <v>287</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>znajder</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4266</v>
+        <v>3.2561</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7922</v>
+        <v>0.7527</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9212</v>
+        <v>0.832</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4266</v>
+        <v>3.2561</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7496</v>
+        <v>2.4166</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.323</v>
+        <v>0.8395</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7496</v>
+        <v>3.0282</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0392</v>
+        <v>1.5745</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.323</v>
+        <v>0.8395</v>
       </c>
       <c r="K7" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L7" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7162</v>
+        <v>2.414</v>
       </c>
       <c r="N7" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.862</v>
+        <v>2.9756</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6616</v>
+        <v>0.6879</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6963</v>
+        <v>0.7053</v>
       </c>
       <c r="E8" t="n">
-        <v>2.862</v>
+        <v>2.9756</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8901</v>
+        <v>2.3173</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9719</v>
+        <v>0.6583</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8901</v>
+        <v>2.6783</v>
       </c>
       <c r="I8" t="n">
-        <v>1.532</v>
+        <v>1.3926</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9719</v>
+        <v>0.6583</v>
       </c>
       <c r="K8" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L8" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5039</v>
+        <v>2.0509</v>
       </c>
       <c r="N8" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8494</v>
+        <v>2.9386</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6587</v>
+        <v>0.6793</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6913</v>
+        <v>0.6886</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8494</v>
+        <v>2.9386</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9489</v>
+        <v>1.3919</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0995</v>
+        <v>1.5467</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9489</v>
+        <v>1.3919</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2007</v>
+        <v>0.7237</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0995</v>
+        <v>1.5467</v>
       </c>
       <c r="K9" t="n">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="L9" t="n">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1012</v>
+        <v>2.2704</v>
       </c>
       <c r="N9" t="n">
-        <v>247</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6523</v>
+        <v>2.9336</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6132</v>
+        <v>0.6782</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6128</v>
+        <v>0.6864</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6523</v>
+        <v>2.9336</v>
       </c>
       <c r="F10" t="n">
-        <v>0.863</v>
+        <v>2.178</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7893</v>
+        <v>0.7556</v>
       </c>
       <c r="H10" t="n">
-        <v>0.863</v>
+        <v>2.1877</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6995</v>
+        <v>1.1375</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7893</v>
+        <v>0.7556</v>
       </c>
       <c r="K10" t="n">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="L10" t="n">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4888</v>
+        <v>1.8931</v>
       </c>
       <c r="N10" t="n">
-        <v>134</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>znajder</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2298</v>
+        <v>2.865</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5155</v>
+        <v>0.6623</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4444</v>
+        <v>0.6554</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2298</v>
+        <v>2.865</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5449</v>
+        <v>3.0444</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6849</v>
+        <v>-0.1794</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5449</v>
+        <v>5.2402</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2522</v>
+        <v>2.7247</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6849</v>
+        <v>-0.1794</v>
       </c>
       <c r="K11" t="n">
         <v>47</v>
@@ -943,7 +943,7 @@
         <v>79</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9371</v>
+        <v>2.5453</v>
       </c>
       <c r="N11" t="n">
         <v>126</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.935</v>
+        <v>2.5493</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4473</v>
+        <v>0.5893</v>
       </c>
       <c r="D12" t="n">
-        <v>0.327</v>
+        <v>0.5129</v>
       </c>
       <c r="E12" t="n">
-        <v>1.935</v>
+        <v>2.5493</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1947</v>
+        <v>3.2815</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7403</v>
+        <v>-0.7322</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1947</v>
+        <v>6.0757</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9683</v>
+        <v>3.1591</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7403</v>
+        <v>-0.7322</v>
       </c>
       <c r="K12" t="n">
         <v>108</v>
@@ -989,7 +989,7 @@
         <v>139</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7086</v>
+        <v>2.4269</v>
       </c>
       <c r="N12" t="n">
         <v>247</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6377</v>
+        <v>2.4838</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3786</v>
+        <v>0.5742</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2085</v>
+        <v>0.4833</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6377</v>
+        <v>2.4838</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4081</v>
+        <v>2.3197</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2296</v>
+        <v>0.1641</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4081</v>
+        <v>2.687</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1413</v>
+        <v>1.3971</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2296</v>
+        <v>0.1641</v>
       </c>
       <c r="K13" t="n">
         <v>108</v>
@@ -1035,7 +1035,7 @@
         <v>139</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3709</v>
+        <v>1.5612</v>
       </c>
       <c r="N13" t="n">
         <v>247</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Friis</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3519</v>
+        <v>2.3188</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3125</v>
+        <v>0.5361</v>
       </c>
       <c r="D14" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.4088</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3519</v>
+        <v>2.3188</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3519</v>
+        <v>2.3047</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.0141</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3519</v>
+        <v>2.6339</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3519</v>
+        <v>1.3695</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.0141</v>
       </c>
       <c r="K14" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3519</v>
+        <v>1.3836</v>
       </c>
       <c r="N14" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.289</v>
+        <v>1.9929</v>
       </c>
       <c r="C15" t="n">
-        <v>0.298</v>
+        <v>0.4607</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0696</v>
+        <v>0.2617</v>
       </c>
       <c r="E15" t="n">
-        <v>1.289</v>
+        <v>1.9929</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0902</v>
+        <v>2.5239</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8012</v>
+        <v>-0.531</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0902</v>
+        <v>3.4065</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6942</v>
+        <v>1.7712</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8012</v>
+        <v>-0.531</v>
       </c>
       <c r="K15" t="n">
         <v>47</v>
@@ -1127,7 +1127,7 @@
         <v>79</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8929999999999999</v>
+        <v>1.2402</v>
       </c>
       <c r="N15" t="n">
         <v>126</v>
@@ -1136,185 +1136,185 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>disco doplan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2221</v>
+        <v>1.4188</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2825</v>
+        <v>0.328</v>
       </c>
       <c r="D16" t="n">
-        <v>0.043</v>
+        <v>0.0025</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2221</v>
+        <v>1.4188</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4797</v>
+        <v>1.4188</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2576</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4797</v>
+        <v>1.4188</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1993</v>
+        <v>1.4188</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2576</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="L16" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9417</v>
+        <v>1.4188</v>
       </c>
       <c r="N16" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>disco doplan</t>
+          <t>Friis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1921</v>
+        <v>1.4048</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2756</v>
+        <v>0.3248</v>
       </c>
       <c r="D17" t="n">
-        <v>0.031</v>
+        <v>-0.0038</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1921</v>
+        <v>1.4048</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1921</v>
+        <v>1.4048</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1921</v>
+        <v>1.4048</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1921</v>
+        <v>1.4048</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1921</v>
+        <v>1.4048</v>
       </c>
       <c r="N17" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>freddieb</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9354</v>
+        <v>1.2304</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2162</v>
+        <v>0.2844</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0712</v>
+        <v>-0.0825</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9354</v>
+        <v>1.2304</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9354</v>
+        <v>1.2304</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9354</v>
+        <v>1.2304</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9354</v>
+        <v>1.2304</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9354</v>
+        <v>1.2304</v>
       </c>
       <c r="N18" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>freddieb</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8421999999999999</v>
+        <v>1.2274</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1947</v>
+        <v>0.2838</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1084</v>
+        <v>-0.0839</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8421999999999999</v>
+        <v>1.2274</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8421999999999999</v>
+        <v>1.2274</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8421999999999999</v>
+        <v>1.2274</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8421999999999999</v>
+        <v>1.2274</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8421999999999999</v>
+        <v>1.2274</v>
       </c>
       <c r="N19" t="n">
-        <v>78</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5677</v>
+        <v>0.7435</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1312</v>
+        <v>0.1719</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2177</v>
+        <v>-0.3024</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5677</v>
+        <v>0.7435</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5677</v>
+        <v>0.7435</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5677</v>
+        <v>0.7435</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5677</v>
+        <v>0.7435</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5677</v>
+        <v>0.7435</v>
       </c>
       <c r="N20" t="n">
         <v>128</v>
@@ -1366,139 +1366,139 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5246</v>
+        <v>0.7411</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1213</v>
+        <v>0.1713</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2349</v>
+        <v>-0.3034</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5246</v>
+        <v>0.7411</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5246</v>
+        <v>1.7411</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5246</v>
+        <v>1.7411</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5246</v>
+        <v>0.9053</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K21" t="n">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5246</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4327</v>
+        <v>0.7119</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1</v>
+        <v>0.1646</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2715</v>
+        <v>-0.3166</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4327</v>
+        <v>0.7119</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4327</v>
+        <v>0.7119</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4327</v>
+        <v>0.7119</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4327</v>
+        <v>0.7119</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4327</v>
+        <v>0.7119</v>
       </c>
       <c r="N22" t="n">
-        <v>75</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2076</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.048</v>
+        <v>0.1579</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3612</v>
+        <v>-0.3297</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2076</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2076</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2076</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9788</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L23" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0212</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>134</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.3976</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0154</v>
+        <v>0.0919</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4174</v>
+        <v>-0.4585</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.3976</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.3976</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.3976</v>
       </c>
       <c r="I24" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.3976</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.3976</v>
       </c>
       <c r="N24" t="n">
         <v>78</v>
@@ -1550,35 +1550,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>pauf</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.133</v>
+        <v>0.2568</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0307</v>
+        <v>0.0594</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4969</v>
+        <v>-0.5221</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.133</v>
+        <v>0.2568</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0776</v>
+        <v>0.4541</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0554</v>
+        <v>-0.1973</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0776</v>
+        <v>0.4541</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0629</v>
+        <v>0.2361</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0554</v>
+        <v>-0.1973</v>
       </c>
       <c r="K25" t="n">
         <v>47</v>
@@ -1587,7 +1587,7 @@
         <v>79</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1183</v>
+        <v>0.0388</v>
       </c>
       <c r="N25" t="n">
         <v>126</v>
@@ -1596,231 +1596,231 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1333</v>
+        <v>0.2093</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0308</v>
+        <v>0.0484</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.497</v>
+        <v>-0.5435</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1333</v>
+        <v>0.2093</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1333</v>
+        <v>0.2069</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1333</v>
+        <v>0.2069</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1333</v>
+        <v>0.1076</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="K26" t="n">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1333</v>
+        <v>0.11</v>
       </c>
       <c r="N26" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1911</v>
+        <v>-0.0484</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0442</v>
+        <v>-0.0112</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.52</v>
+        <v>-0.6599</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1911</v>
+        <v>-0.0484</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.2996</v>
+        <v>-0.0484</v>
       </c>
       <c r="G27" t="n">
-        <v>2.1085</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.2996</v>
+        <v>-0.0484</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.8639</v>
+        <v>-0.0484</v>
       </c>
       <c r="J27" t="n">
-        <v>2.1085</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="L27" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2445999999999999</v>
+        <v>-0.0484</v>
       </c>
       <c r="N27" t="n">
-        <v>287</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pauf</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2449</v>
+        <v>-0.0488</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0566</v>
+        <v>-0.0113</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5415</v>
+        <v>-0.66</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2449</v>
+        <v>-0.0488</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1659</v>
+        <v>-0.0488</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4108</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1659</v>
+        <v>-0.0488</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1345</v>
+        <v>-0.0488</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4108</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="L28" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2763</v>
+        <v>-0.0488</v>
       </c>
       <c r="N28" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2726</v>
+        <v>-0.1468</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.063</v>
+        <v>-0.0339</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5525</v>
+        <v>-0.7043</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2726</v>
+        <v>-0.1468</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2726</v>
+        <v>-0.1468</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2726</v>
+        <v>-0.1468</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2726</v>
+        <v>-0.1468</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2726</v>
+        <v>-0.1468</v>
       </c>
       <c r="N29" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2797</v>
+        <v>-0.1655</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0383</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5553</v>
+        <v>-0.7127</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2797</v>
+        <v>-0.1655</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2797</v>
+        <v>-0.1655</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2797</v>
+        <v>-0.1655</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2797</v>
+        <v>-0.1655</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2797</v>
+        <v>-0.1655</v>
       </c>
       <c r="N30" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.463</v>
+        <v>-0.1919</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.107</v>
+        <v>-0.0444</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6284</v>
+        <v>-0.7246</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.463</v>
+        <v>-0.1919</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.463</v>
+        <v>-0.1919</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.463</v>
+        <v>-0.1919</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.463</v>
+        <v>-0.1919</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.463</v>
+        <v>-0.1919</v>
       </c>
       <c r="N31" t="n">
         <v>128</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5429</v>
+        <v>-0.3798</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1255</v>
+        <v>-0.0878</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6602</v>
+        <v>-0.8095</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5429</v>
+        <v>-0.3798</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5429</v>
+        <v>-2.3775</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1.9977</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5429</v>
+        <v>-2.3775</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5429</v>
+        <v>-1.2362</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1.9977</v>
       </c>
       <c r="K32" t="n">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5429</v>
+        <v>0.7615000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>75</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5433</v>
+        <v>-0.3927</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1256</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6604</v>
+        <v>-0.8153</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5433</v>
+        <v>-0.3927</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5433</v>
+        <v>-0.3927</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5433</v>
+        <v>-0.3927</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5433</v>
+        <v>-0.3927</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5433</v>
+        <v>-0.3927</v>
       </c>
       <c r="N33" t="n">
-        <v>139</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6221</v>
+        <v>-0.3958</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1438</v>
+        <v>-0.0915</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6918</v>
+        <v>-0.8167</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6221</v>
+        <v>-0.3958</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6221</v>
+        <v>-0.3958</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6221</v>
+        <v>-0.3958</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6221</v>
+        <v>-0.3958</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6221</v>
+        <v>-0.3958</v>
       </c>
       <c r="N34" t="n">
         <v>78</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>juho</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0019</v>
+        <v>-0.421</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2316</v>
+        <v>-0.0973</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8431</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0019</v>
+        <v>-0.421</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0019</v>
+        <v>-0.1823</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.2387</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0019</v>
+        <v>-0.1823</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0019</v>
+        <v>-0.0948</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.2387</v>
       </c>
       <c r="K35" t="n">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0019</v>
+        <v>-0.3335</v>
       </c>
       <c r="N35" t="n">
-        <v>75</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>juho</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0468</v>
+        <v>-0.6857</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.242</v>
+        <v>-0.1585</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.861</v>
+        <v>-0.9476</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0468</v>
+        <v>-0.6857</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5121</v>
+        <v>-0.6857</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5347</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5121</v>
+        <v>-0.6857</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4151</v>
+        <v>-0.6857</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5347</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="L36" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9498</v>
+        <v>-0.6857</v>
       </c>
       <c r="N36" t="n">
-        <v>247</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0906</v>
+        <v>-0.7397</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2521</v>
+        <v>-0.171</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8784</v>
+        <v>-0.972</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0906</v>
+        <v>-0.7397</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0906</v>
+        <v>-0.7397</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0906</v>
+        <v>-0.7397</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0906</v>
+        <v>-0.7397</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0906</v>
+        <v>-0.7397</v>
       </c>
       <c r="N37" t="n">
         <v>75</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1704</v>
+        <v>-0.7941</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2706</v>
+        <v>-0.1836</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9102</v>
+        <v>-0.9965000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1704</v>
+        <v>-0.7941</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1704</v>
+        <v>-0.7941</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1704</v>
+        <v>-0.7941</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1704</v>
+        <v>-0.7941</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1704</v>
+        <v>-0.7941</v>
       </c>
       <c r="N38" t="n">
         <v>75</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>xelos</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2993</v>
+        <v>-0.8993</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3004</v>
+        <v>-0.2079</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9616</v>
+        <v>-1.044</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2993</v>
+        <v>-0.8993</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2993</v>
+        <v>-0.8993</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2993</v>
+        <v>-0.8993</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2993</v>
+        <v>-0.8993</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2993</v>
+        <v>-0.8993</v>
       </c>
       <c r="N39" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>xelos</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3814</v>
+        <v>-1.0493</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3194</v>
+        <v>-0.2426</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9943</v>
+        <v>-1.1117</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3814</v>
+        <v>-1.0493</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3814</v>
+        <v>-1.0493</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3814</v>
+        <v>-1.0493</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3814</v>
+        <v>-1.0493</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3814</v>
+        <v>-1.0493</v>
       </c>
       <c r="N40" t="n">
-        <v>78</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6832</v>
+        <v>-2.0752</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3891</v>
+        <v>-0.4797</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1145</v>
+        <v>-1.5749</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6832</v>
+        <v>-2.0752</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7429</v>
+        <v>-2.2712</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0597</v>
+        <v>0.196</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7429</v>
+        <v>-2.2712</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4127</v>
+        <v>-1.1809</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0597</v>
+        <v>0.196</v>
       </c>
       <c r="K41" t="n">
         <v>108</v>
@@ -2323,7 +2323,7 @@
         <v>139</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.353</v>
+        <v>-0.9849000000000001</v>
       </c>
       <c r="N41" t="n">
         <v>247</v>
@@ -2429,10 +2429,10 @@
         <v>1.65</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4885</v>
+        <v>1.3171</v>
       </c>
       <c r="J2" t="n">
-        <v>38.701</v>
+        <v>34.2446</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.25</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6286</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>16.3436</v>
+        <v>17.3914</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5647</v>
+        <v>0.6236</v>
       </c>
       <c r="J4" t="n">
-        <v>14.6822</v>
+        <v>16.2136</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2146</v>
+        <v>0.2912</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5796</v>
+        <v>7.5712</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0818</v>
+        <v>-0.0056</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.1268</v>
+        <v>-0.1456</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1948</v>
+        <v>0.1827</v>
       </c>
       <c r="J7" t="n">
-        <v>5.0648</v>
+        <v>4.7502</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0722</v>
+        <v>0.0354</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8772</v>
+        <v>0.9204</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3217</v>
+        <v>-0.2113</v>
       </c>
       <c r="J9" t="n">
-        <v>-8.3642</v>
+        <v>-5.4938</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.71</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4731</v>
+        <v>-0.3085</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.3006</v>
+        <v>-8.021000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4871</v>
+        <v>-0.3181</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.6646</v>
+        <v>-8.2706</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0345</v>
+        <v>1.0258</v>
       </c>
       <c r="J12" t="n">
-        <v>30.0005</v>
+        <v>29.7482</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.8495</v>
       </c>
       <c r="J13" t="n">
-        <v>24.2208</v>
+        <v>24.6355</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.22</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.6005</v>
       </c>
       <c r="J14" t="n">
-        <v>15.6252</v>
+        <v>17.4145</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3793</v>
+        <v>0.4529</v>
       </c>
       <c r="J15" t="n">
-        <v>10.9997</v>
+        <v>13.1341</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2154</v>
+        <v>0.2917</v>
       </c>
       <c r="J16" t="n">
-        <v>6.2466</v>
+        <v>8.459300000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.11</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3019</v>
+        <v>0.3191</v>
       </c>
       <c r="J17" t="n">
-        <v>8.755100000000001</v>
+        <v>9.2539</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.88</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1822</v>
+        <v>-0.141</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.2838</v>
+        <v>-4.089</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2661</v>
+        <v>-0.1813</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.7169</v>
+        <v>-5.2577</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.74</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4287</v>
+        <v>-0.2792</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.4323</v>
+        <v>-8.0968</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.68</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.3365</v>
       </c>
       <c r="J21" t="n">
-        <v>-14.8944</v>
+        <v>-9.7585</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.35</v>
       </c>
       <c r="I22" t="n">
-        <v>0.593</v>
+        <v>0.5581</v>
       </c>
       <c r="J22" t="n">
-        <v>16.604</v>
+        <v>15.6268</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3488</v>
+        <v>0.3677</v>
       </c>
       <c r="J23" t="n">
-        <v>9.766400000000001</v>
+        <v>10.2956</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0551</v>
+        <v>0.042</v>
       </c>
       <c r="J24" t="n">
-        <v>1.5428</v>
+        <v>1.176</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.71</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5022</v>
+        <v>-0.3237</v>
       </c>
       <c r="J25" t="n">
-        <v>-14.0616</v>
+        <v>-9.063599999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.63</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6049</v>
+        <v>-0.3989</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.9372</v>
+        <v>-11.1692</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.35</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9343</v>
+        <v>0.6825</v>
       </c>
       <c r="J27" t="n">
-        <v>26.1604</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.25</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7027</v>
+        <v>0.5444</v>
       </c>
       <c r="J28" t="n">
-        <v>19.6756</v>
+        <v>15.2432</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.5017</v>
       </c>
       <c r="J29" t="n">
-        <v>17.57</v>
+        <v>14.0476</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.97</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2417</v>
+        <v>-0.1686</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.7676</v>
+        <v>-4.7208</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.95</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3101</v>
+        <v>-0.237</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.6828</v>
+        <v>-6.636</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.57</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7542</v>
+        <v>0.5374</v>
       </c>
       <c r="J32" t="n">
-        <v>19.6092</v>
+        <v>13.9724</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.53</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7091</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>18.4366</v>
+        <v>13.3276</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.5</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6745</v>
+        <v>0.4939</v>
       </c>
       <c r="J34" t="n">
-        <v>17.537</v>
+        <v>12.8414</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.98</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1464</v>
+        <v>-0.065</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.8064</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.92</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2571</v>
+        <v>-0.1417</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.6846</v>
+        <v>-3.6842</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.96</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0057</v>
+        <v>-0.0353</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1482</v>
+        <v>-0.9177999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.85</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2052</v>
+        <v>-0.1651</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.3352</v>
+        <v>-4.2926</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.77</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3575</v>
+        <v>-0.2431</v>
       </c>
       <c r="J39" t="n">
-        <v>-9.295</v>
+        <v>-6.3206</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.77</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3575</v>
+        <v>-0.2431</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.295</v>
+        <v>-6.3206</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.62</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5795</v>
+        <v>-0.3851</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.067</v>
+        <v>-10.0126</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4872</v>
+        <v>0.476</v>
       </c>
       <c r="J42" t="n">
-        <v>14.616</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.21</v>
       </c>
       <c r="I43" t="n">
-        <v>0.391</v>
+        <v>0.4028</v>
       </c>
       <c r="J43" t="n">
-        <v>11.73</v>
+        <v>12.084</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.16</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3172</v>
+        <v>0.348</v>
       </c>
       <c r="J44" t="n">
-        <v>9.516</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0514</v>
+        <v>-0.0221</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.542</v>
+        <v>-0.663</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.46</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8112</v>
+        <v>-0.5565</v>
       </c>
       <c r="J46" t="n">
-        <v>-24.336</v>
+        <v>-16.695</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.4</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0648</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>31.944</v>
+        <v>22.818</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.11</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3423</v>
+        <v>0.3417</v>
       </c>
       <c r="J48" t="n">
-        <v>10.269</v>
+        <v>10.251</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.08</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2324</v>
+        <v>0.2663</v>
       </c>
       <c r="J49" t="n">
-        <v>6.972</v>
+        <v>7.989</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.1425</v>
       </c>
       <c r="J50" t="n">
-        <v>2.886</v>
+        <v>4.275</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.9</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4447</v>
+        <v>-0.3789</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.341</v>
+        <v>-11.367</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3511</v>
+        <v>0.3632</v>
       </c>
       <c r="J52" t="n">
-        <v>9.479699999999999</v>
+        <v>9.8064</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1063</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.8701</v>
+        <v>-2.5839</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.8</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3345</v>
+        <v>-0.2202</v>
       </c>
       <c r="J54" t="n">
-        <v>-9.031499999999999</v>
+        <v>-5.9454</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4987</v>
+        <v>-0.3265</v>
       </c>
       <c r="J55" t="n">
-        <v>-13.4649</v>
+        <v>-8.8155</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5125</v>
+        <v>-0.336</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.8375</v>
+        <v>-9.071999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.53</v>
       </c>
       <c r="I57" t="n">
-        <v>1.228</v>
+        <v>0.8812</v>
       </c>
       <c r="J57" t="n">
-        <v>33.156</v>
+        <v>23.7924</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.35</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8411</v>
+        <v>0.6551</v>
       </c>
       <c r="J58" t="n">
-        <v>22.7097</v>
+        <v>17.6877</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.24</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5497</v>
+        <v>0.5115</v>
       </c>
       <c r="J59" t="n">
-        <v>14.8419</v>
+        <v>13.8105</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.23</v>
       </c>
       <c r="I60" t="n">
-        <v>0.525</v>
+        <v>0.4975</v>
       </c>
       <c r="J60" t="n">
-        <v>14.175</v>
+        <v>13.4325</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.21</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4755</v>
+        <v>0.4692</v>
       </c>
       <c r="J61" t="n">
-        <v>12.8385</v>
+        <v>12.6684</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.6</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.5552</v>
       </c>
       <c r="J62" t="n">
-        <v>22.0024</v>
+        <v>15.5456</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.48</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6493</v>
+        <v>0.4808</v>
       </c>
       <c r="J63" t="n">
-        <v>18.1804</v>
+        <v>13.4624</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.29</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3908</v>
+        <v>0.3596</v>
       </c>
       <c r="J64" t="n">
-        <v>10.9424</v>
+        <v>10.0688</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.23</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3035</v>
+        <v>0.3079</v>
       </c>
       <c r="J65" t="n">
-        <v>8.497999999999999</v>
+        <v>8.6212</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2414</v>
+        <v>-0.1305</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.7592</v>
+        <v>-3.654</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2966</v>
+        <v>0.237</v>
       </c>
       <c r="J67" t="n">
-        <v>8.3048</v>
+        <v>6.636</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.86</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1819</v>
+        <v>-0.1525</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.0932</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.72</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4326</v>
+        <v>-0.289</v>
       </c>
       <c r="J69" t="n">
-        <v>-12.1128</v>
+        <v>-8.092000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.63</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5625</v>
+        <v>-0.374</v>
       </c>
       <c r="J70" t="n">
-        <v>-15.75</v>
+        <v>-10.472</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.61</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5895</v>
+        <v>-0.3927</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.506</v>
+        <v>-10.9956</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.97</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0303</v>
+        <v>-0.0128</v>
       </c>
       <c r="J72" t="n">
-        <v>0.7272</v>
+        <v>-0.3072</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.79</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2891</v>
+        <v>-0.2209</v>
       </c>
       <c r="J73" t="n">
-        <v>-6.9384</v>
+        <v>-5.3016</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.75</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3702</v>
+        <v>-0.2582</v>
       </c>
       <c r="J74" t="n">
-        <v>-8.8848</v>
+        <v>-6.1968</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4535</v>
+        <v>-0.3048</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.884</v>
+        <v>-7.3152</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.59</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6101</v>
+        <v>-0.4081</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.6424</v>
+        <v>-9.7944</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>1.1756</v>
+        <v>0.8428</v>
       </c>
       <c r="J77" t="n">
-        <v>28.2144</v>
+        <v>20.2272</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.48</v>
       </c>
       <c r="I78" t="n">
-        <v>1.1553</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>27.7272</v>
+        <v>19.9224</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>0.533</v>
+        <v>0.4902</v>
       </c>
       <c r="J79" t="n">
-        <v>12.792</v>
+        <v>11.7648</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.06</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0941</v>
+        <v>0.171</v>
       </c>
       <c r="J80" t="n">
-        <v>2.2584</v>
+        <v>4.104</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.02</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0422</v>
+        <v>0.0341</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.0128</v>
+        <v>0.8184</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.45</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1553</v>
+        <v>1.094</v>
       </c>
       <c r="J82" t="n">
-        <v>33.5037</v>
+        <v>31.726</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.38</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0082</v>
+        <v>0.9905</v>
       </c>
       <c r="J83" t="n">
-        <v>29.2378</v>
+        <v>28.7245</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.03</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0454</v>
+        <v>0.1015</v>
       </c>
       <c r="J84" t="n">
-        <v>1.3166</v>
+        <v>2.9435</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.98</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1971</v>
+        <v>-0.1272</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.7159</v>
+        <v>-3.6888</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6634</v>
+        <v>-0.606</v>
       </c>
       <c r="J86" t="n">
-        <v>-19.2386</v>
+        <v>-17.574</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.13</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2834</v>
+        <v>0.3108</v>
       </c>
       <c r="J87" t="n">
-        <v>8.2186</v>
+        <v>9.013199999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.01</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0499</v>
+        <v>0.0402</v>
       </c>
       <c r="J88" t="n">
-        <v>1.4471</v>
+        <v>1.1658</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0837</v>
+        <v>-0.0487</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.4273</v>
+        <v>-1.4123</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1284</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.7236</v>
+        <v>-2.1576</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2889</v>
+        <v>-0.1756</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.3781</v>
+        <v>-5.0924</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.27</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7843</v>
+        <v>0.759</v>
       </c>
       <c r="J92" t="n">
-        <v>23.529</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6881</v>
+        <v>0.6611</v>
       </c>
       <c r="J93" t="n">
-        <v>20.643</v>
+        <v>19.833</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3911</v>
+        <v>0.3786</v>
       </c>
       <c r="J94" t="n">
-        <v>11.733</v>
+        <v>11.358</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.97</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2161</v>
+        <v>-0.1532</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.483</v>
+        <v>-4.596</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.86</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.4872</v>
       </c>
       <c r="J96" t="n">
-        <v>-16.437</v>
+        <v>-14.616</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.31</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5279</v>
+        <v>0.6284</v>
       </c>
       <c r="J97" t="n">
-        <v>15.837</v>
+        <v>18.852</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1861</v>
+        <v>0.2014</v>
       </c>
       <c r="J98" t="n">
-        <v>5.583</v>
+        <v>6.042</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.013</v>
+        <v>-0.001</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.39</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.86</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2977</v>
+        <v>-0.1793</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.930999999999999</v>
+        <v>-5.379</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.83</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3434</v>
+        <v>-0.2105</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.302</v>
+        <v>-6.315</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.78</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9769</v>
+        <v>0.8952</v>
       </c>
       <c r="J102" t="n">
-        <v>21.4918</v>
+        <v>19.6944</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.44</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6025</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>13.255</v>
+        <v>11.8976</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.33</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4593</v>
+        <v>0.4212</v>
       </c>
       <c r="J104" t="n">
-        <v>10.1046</v>
+        <v>9.266400000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.13</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1583</v>
+        <v>0.1818</v>
       </c>
       <c r="J105" t="n">
-        <v>3.4826</v>
+        <v>3.9996</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3916</v>
+        <v>-0.2385</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.6152</v>
+        <v>-5.247</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.02</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1302</v>
+        <v>0.0793</v>
       </c>
       <c r="J107" t="n">
-        <v>2.8644</v>
+        <v>1.7446</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.97</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0122</v>
+        <v>-0.034</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.2684</v>
+        <v>-0.748</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2276</v>
+        <v>-0.1623</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.0072</v>
+        <v>-3.5706</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.84</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2715</v>
+        <v>-0.182</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.973</v>
+        <v>-4.004</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.6</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6211</v>
+        <v>-0.4127</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.6642</v>
+        <v>-9.0794</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.15</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3681</v>
+        <v>0.4059</v>
       </c>
       <c r="J112" t="n">
-        <v>9.202500000000001</v>
+        <v>10.1475</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.9</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1413</v>
+        <v>-0.1181</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.5325</v>
+        <v>-2.9525</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.76</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.396</v>
+        <v>-0.2587</v>
       </c>
       <c r="J114" t="n">
-        <v>-9.9</v>
+        <v>-6.4675</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.426</v>
+        <v>-0.2781</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.65</v>
+        <v>-6.9525</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.66</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5387</v>
+        <v>-0.3544</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.4675</v>
+        <v>-8.859999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.73</v>
       </c>
       <c r="I117" t="n">
-        <v>1.6295</v>
+        <v>1.4113</v>
       </c>
       <c r="J117" t="n">
-        <v>40.7375</v>
+        <v>35.2825</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.55</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2921</v>
+        <v>1.1905</v>
       </c>
       <c r="J118" t="n">
-        <v>32.3025</v>
+        <v>29.7625</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.29</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7292</v>
+        <v>0.7568</v>
       </c>
       <c r="J119" t="n">
-        <v>18.23</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.378</v>
+        <v>-0.2973</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.449999999999999</v>
+        <v>-7.4325</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7669</v>
+        <v>-0.7145</v>
       </c>
       <c r="J121" t="n">
-        <v>-19.1725</v>
+        <v>-17.8625</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.08</v>
       </c>
       <c r="I122" t="n">
-        <v>0.249</v>
+        <v>0.2512</v>
       </c>
       <c r="J122" t="n">
-        <v>5.976</v>
+        <v>6.0288</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.95</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0531</v>
+        <v>-0.0606</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.2744</v>
+        <v>-1.4544</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.82</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3058</v>
+        <v>-0.2016</v>
       </c>
       <c r="J124" t="n">
-        <v>-7.3392</v>
+        <v>-4.8384</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3226</v>
+        <v>-0.2115</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.7424</v>
+        <v>-5.076</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.62</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.595</v>
+        <v>-0.3938</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.28</v>
+        <v>-9.4512</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.42</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0785</v>
+        <v>1.0464</v>
       </c>
       <c r="J127" t="n">
-        <v>25.884</v>
+        <v>25.1136</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6705</v>
+        <v>0.6637</v>
       </c>
       <c r="J128" t="n">
-        <v>16.092</v>
+        <v>15.9288</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.17</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4803</v>
+        <v>0.4936</v>
       </c>
       <c r="J129" t="n">
-        <v>11.5272</v>
+        <v>11.8464</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.14</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3777</v>
+        <v>0.4191</v>
       </c>
       <c r="J130" t="n">
-        <v>9.0648</v>
+        <v>10.0584</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.83</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6468</v>
+        <v>-0.5868</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.5232</v>
+        <v>-14.0832</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.42</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0858</v>
+        <v>1.0501</v>
       </c>
       <c r="J132" t="n">
-        <v>28.2308</v>
+        <v>27.3026</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.21</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6029</v>
+        <v>0.5948</v>
       </c>
       <c r="J133" t="n">
-        <v>15.6754</v>
+        <v>15.4648</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3915</v>
+        <v>0.4214</v>
       </c>
       <c r="J134" t="n">
-        <v>10.179</v>
+        <v>10.9564</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.14</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3915</v>
+        <v>0.4214</v>
       </c>
       <c r="J135" t="n">
-        <v>10.179</v>
+        <v>10.9564</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.82</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6675</v>
+        <v>-0.6096</v>
       </c>
       <c r="J136" t="n">
-        <v>-17.355</v>
+        <v>-15.8496</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.35</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6049</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="J137" t="n">
-        <v>15.7274</v>
+        <v>18.9878</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1213</v>
+        <v>-0.0829</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.1538</v>
+        <v>-2.1554</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2234</v>
+        <v>-0.1386</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.8084</v>
+        <v>-3.6036</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.258</v>
+        <v>-0.16</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.708</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.65</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5737</v>
+        <v>-0.3763</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.9162</v>
+        <v>-9.783799999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.26</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7953</v>
+        <v>0.7598</v>
       </c>
       <c r="J142" t="n">
-        <v>23.0637</v>
+        <v>22.0342</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.03</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1246</v>
+        <v>0.1242</v>
       </c>
       <c r="J143" t="n">
-        <v>3.6134</v>
+        <v>3.6018</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0352</v>
+        <v>-0.0056</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.0208</v>
+        <v>-0.1624</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.97</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1825</v>
+        <v>-0.1374</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.2925</v>
+        <v>-3.9846</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.89</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.441</v>
+        <v>-0.3862</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.789</v>
+        <v>-11.1998</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.39</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.7484</v>
       </c>
       <c r="J147" t="n">
-        <v>17.8466</v>
+        <v>21.7036</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.14</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2725</v>
+        <v>0.3118</v>
       </c>
       <c r="J148" t="n">
-        <v>7.9025</v>
+        <v>9.042199999999999</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0994</v>
+        <v>0.1311</v>
       </c>
       <c r="J149" t="n">
-        <v>2.8826</v>
+        <v>3.8019</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.97</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.114</v>
+        <v>-0.0555</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.306</v>
+        <v>-1.6095</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.73</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4908</v>
+        <v>-0.3138</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.2332</v>
+        <v>-9.100199999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.32</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5515</v>
+        <v>0.6583</v>
       </c>
       <c r="J152" t="n">
-        <v>16.545</v>
+        <v>19.749</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.97</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0837</v>
+        <v>-0.0487</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.511</v>
+        <v>-1.461</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.93</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1682</v>
+        <v>-0.0984</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.046</v>
+        <v>-2.952</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.87</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2728</v>
+        <v>-0.165</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.183999999999999</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.83</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3354</v>
+        <v>-0.2068</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.062</v>
+        <v>-6.204</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.35</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9107</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>27.321</v>
+        <v>27.294</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.32</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8429</v>
+        <v>0.8418</v>
       </c>
       <c r="J158" t="n">
-        <v>25.287</v>
+        <v>25.254</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.2</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5391</v>
+        <v>0.5611</v>
       </c>
       <c r="J159" t="n">
-        <v>16.173</v>
+        <v>16.833</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.18</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4699</v>
+        <v>0.5137</v>
       </c>
       <c r="J160" t="n">
-        <v>14.097</v>
+        <v>15.411</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.91</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4458</v>
+        <v>-0.3722</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.374</v>
+        <v>-11.166</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.99</v>
       </c>
       <c r="I162" t="n">
-        <v>0.035</v>
+        <v>-0.0034</v>
       </c>
       <c r="J162" t="n">
-        <v>0.805</v>
+        <v>-0.07820000000000001</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.9</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1505</v>
+        <v>-0.1205</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.4615</v>
+        <v>-2.7715</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.88</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1882</v>
+        <v>-0.1421</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.3286</v>
+        <v>-3.2683</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3874</v>
+        <v>-0.2514</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.9102</v>
+        <v>-5.7822</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.76</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4025</v>
+        <v>-0.2611</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.2575</v>
+        <v>-6.0053</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.55</v>
       </c>
       <c r="I167" t="n">
-        <v>1.294</v>
+        <v>1.1914</v>
       </c>
       <c r="J167" t="n">
-        <v>29.762</v>
+        <v>27.4022</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.55</v>
       </c>
       <c r="I168" t="n">
-        <v>1.294</v>
+        <v>1.1914</v>
       </c>
       <c r="J168" t="n">
-        <v>29.762</v>
+        <v>27.4022</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.13</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2942</v>
+        <v>0.372</v>
       </c>
       <c r="J169" t="n">
-        <v>6.7666</v>
+        <v>8.555999999999999</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.08</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1537</v>
+        <v>0.2314</v>
       </c>
       <c r="J170" t="n">
-        <v>3.5351</v>
+        <v>5.3222</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.279</v>
+        <v>-0.1958</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.417</v>
+        <v>-4.5034</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.07</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2686</v>
+        <v>0.2727</v>
       </c>
       <c r="J172" t="n">
-        <v>6.4464</v>
+        <v>6.5448</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.85</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1909</v>
+        <v>-0.1604</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.5816</v>
+        <v>-3.8496</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3922</v>
+        <v>-0.2681</v>
       </c>
       <c r="J174" t="n">
-        <v>-9.412800000000001</v>
+        <v>-6.4344</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.65</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5295</v>
+        <v>-0.3528</v>
       </c>
       <c r="J175" t="n">
-        <v>-12.708</v>
+        <v>-8.4672</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.52</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7026</v>
+        <v>-0.4742</v>
       </c>
       <c r="J176" t="n">
-        <v>-16.8624</v>
+        <v>-11.3808</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.55</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2592</v>
+        <v>1.1762</v>
       </c>
       <c r="J177" t="n">
-        <v>30.2208</v>
+        <v>28.2288</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.36</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8528</v>
+        <v>0.8973</v>
       </c>
       <c r="J178" t="n">
-        <v>20.4672</v>
+        <v>21.5352</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.29</v>
       </c>
       <c r="I179" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.7466</v>
       </c>
       <c r="J179" t="n">
-        <v>15.9072</v>
+        <v>17.9184</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.7466</v>
       </c>
       <c r="J180" t="n">
-        <v>15.9072</v>
+        <v>17.9184</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.16</v>
       </c>
       <c r="I181" t="n">
-        <v>0.3428</v>
+        <v>0.4343</v>
       </c>
       <c r="J181" t="n">
-        <v>8.2272</v>
+        <v>10.4232</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.6</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4124</v>
+        <v>1.2654</v>
       </c>
       <c r="J182" t="n">
-        <v>39.5472</v>
+        <v>35.4312</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.48</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1769</v>
+        <v>1.1134</v>
       </c>
       <c r="J183" t="n">
-        <v>32.9532</v>
+        <v>31.1752</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.18</v>
       </c>
       <c r="I184" t="n">
-        <v>0.455</v>
+        <v>0.5107</v>
       </c>
       <c r="J184" t="n">
-        <v>12.74</v>
+        <v>14.2996</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4791</v>
+        <v>-0.406</v>
       </c>
       <c r="J185" t="n">
-        <v>-13.4148</v>
+        <v>-11.368</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.89</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5064</v>
+        <v>-0.4347</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.1792</v>
+        <v>-12.1716</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.08</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2209</v>
+        <v>0.2247</v>
       </c>
       <c r="J187" t="n">
-        <v>6.1852</v>
+        <v>6.2916</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.98</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0203</v>
+        <v>-0.0298</v>
       </c>
       <c r="J188" t="n">
-        <v>-0.5684</v>
+        <v>-0.8344</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.98</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0203</v>
+        <v>-0.0298</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.5684</v>
+        <v>-0.8344</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.92</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1593</v>
+        <v>-0.1046</v>
       </c>
       <c r="J190" t="n">
-        <v>-4.4604</v>
+        <v>-2.9288</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5323</v>
+        <v>-0.3467</v>
       </c>
       <c r="J191" t="n">
-        <v>-14.9044</v>
+        <v>-9.707599999999999</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.27</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5409</v>
+        <v>0.6428</v>
       </c>
       <c r="J192" t="n">
-        <v>12.4407</v>
+        <v>14.7844</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.84</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2501</v>
+        <v>-0.1803</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.7523</v>
+        <v>-4.1469</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.77</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3781</v>
+        <v>-0.2483</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.696300000000001</v>
+        <v>-5.7109</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.74</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4238</v>
+        <v>-0.2773</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.747400000000001</v>
+        <v>-6.3779</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6672</v>
+        <v>-0.4469</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.3456</v>
+        <v>-10.2787</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.86</v>
       </c>
       <c r="I197" t="n">
-        <v>1.8603</v>
+        <v>1.5697</v>
       </c>
       <c r="J197" t="n">
-        <v>42.7869</v>
+        <v>36.1031</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.42</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0314</v>
+        <v>1.0246</v>
       </c>
       <c r="J198" t="n">
-        <v>23.7222</v>
+        <v>23.5658</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.24</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5894</v>
+        <v>0.646</v>
       </c>
       <c r="J199" t="n">
-        <v>13.5562</v>
+        <v>14.858</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.93</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4057</v>
+        <v>-0.3267</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.331099999999999</v>
+        <v>-7.5141</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7183</v>
+        <v>-0.6612</v>
       </c>
       <c r="J201" t="n">
-        <v>-16.5209</v>
+        <v>-15.2076</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.32</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5508</v>
+        <v>0.6574</v>
       </c>
       <c r="J202" t="n">
-        <v>15.9732</v>
+        <v>19.0646</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.05</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1415</v>
+        <v>0.1422</v>
       </c>
       <c r="J203" t="n">
-        <v>4.1035</v>
+        <v>4.1238</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.04</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1209</v>
+        <v>0.1189</v>
       </c>
       <c r="J204" t="n">
-        <v>3.5061</v>
+        <v>3.4481</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4089</v>
+        <v>-0.2573</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.8581</v>
+        <v>-7.4617</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.74</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4644</v>
+        <v>-0.2964</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.4676</v>
+        <v>-8.595599999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.36</v>
       </c>
       <c r="I207" t="n">
-        <v>0.9756</v>
+        <v>0.959</v>
       </c>
       <c r="J207" t="n">
-        <v>28.2924</v>
+        <v>27.811</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.32</v>
       </c>
       <c r="I208" t="n">
-        <v>0.887</v>
+        <v>0.8697</v>
       </c>
       <c r="J208" t="n">
-        <v>25.723</v>
+        <v>25.2213</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.11</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3297</v>
+        <v>0.3483</v>
       </c>
       <c r="J209" t="n">
-        <v>9.561299999999999</v>
+        <v>10.1007</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.02</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0171</v>
+        <v>0.0696</v>
       </c>
       <c r="J210" t="n">
-        <v>0.4959</v>
+        <v>2.0184</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.75</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.8238</v>
+        <v>-0.7804</v>
       </c>
       <c r="J211" t="n">
-        <v>-23.8902</v>
+        <v>-22.6316</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.5</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2006</v>
+        <v>1.1313</v>
       </c>
       <c r="J212" t="n">
-        <v>30.015</v>
+        <v>28.2825</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.41</v>
       </c>
       <c r="I213" t="n">
-        <v>1.0142</v>
+        <v>1.0108</v>
       </c>
       <c r="J213" t="n">
-        <v>25.355</v>
+        <v>25.27</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.34</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8594000000000001</v>
+        <v>0.8724</v>
       </c>
       <c r="J214" t="n">
-        <v>21.485</v>
+        <v>21.81</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.02</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0388</v>
+        <v>0.0365</v>
       </c>
       <c r="J215" t="n">
-        <v>-0.97</v>
+        <v>0.9125</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.95</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3423</v>
+        <v>-0.2613</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.557499999999999</v>
+        <v>-6.5325</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.19</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4314</v>
+        <v>0.4913</v>
       </c>
       <c r="J217" t="n">
-        <v>10.785</v>
+        <v>12.2825</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.96</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0222</v>
+        <v>-0.0431</v>
       </c>
       <c r="J218" t="n">
-        <v>-0.555</v>
+        <v>-1.0775</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.76</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.392</v>
+        <v>-0.2574</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.800000000000001</v>
+        <v>-6.435</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.64</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5629</v>
+        <v>-0.3718</v>
       </c>
       <c r="J220" t="n">
-        <v>-14.0725</v>
+        <v>-9.295</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.61</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6024</v>
+        <v>-0.3999</v>
       </c>
       <c r="J221" t="n">
-        <v>-15.06</v>
+        <v>-9.9975</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4579</v>
+        <v>1.3113</v>
       </c>
       <c r="J222" t="n">
-        <v>32.0738</v>
+        <v>28.8486</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.55</v>
       </c>
       <c r="I223" t="n">
-        <v>1.2059</v>
+        <v>1.1584</v>
       </c>
       <c r="J223" t="n">
-        <v>26.5298</v>
+        <v>25.4848</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.45</v>
       </c>
       <c r="I224" t="n">
-        <v>0.9864000000000001</v>
+        <v>1.0383</v>
       </c>
       <c r="J224" t="n">
-        <v>21.7008</v>
+        <v>22.8426</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.35</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7443</v>
+        <v>0.8588</v>
       </c>
       <c r="J225" t="n">
-        <v>16.3746</v>
+        <v>18.8936</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.18</v>
       </c>
       <c r="I226" t="n">
-        <v>0.3551</v>
+        <v>0.4611</v>
       </c>
       <c r="J226" t="n">
-        <v>7.8122</v>
+        <v>10.1442</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.05</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2686</v>
+        <v>0.2761</v>
       </c>
       <c r="J227" t="n">
-        <v>5.9092</v>
+        <v>6.0742</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.78</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.264</v>
+        <v>-0.2178</v>
       </c>
       <c r="J228" t="n">
-        <v>-5.808</v>
+        <v>-4.7916</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.65</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.4942</v>
+        <v>-0.3406</v>
       </c>
       <c r="J229" t="n">
-        <v>-10.8724</v>
+        <v>-7.4932</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.48</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.7342</v>
+        <v>-0.4992</v>
       </c>
       <c r="J230" t="n">
-        <v>-16.1524</v>
+        <v>-10.9824</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.47</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7471</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J231" t="n">
-        <v>-16.4362</v>
+        <v>-11.1892</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2109/event_2109_evp_summary.xlsx
+++ b/database/event/2109/event_2109_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.401</v>
+        <v>6.3711</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4798</v>
+        <v>1.4729</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2517</v>
+        <v>2.2761</v>
       </c>
       <c r="E2" t="n">
-        <v>6.401</v>
+        <v>6.3711</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9586</v>
+        <v>3.8327</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4424</v>
+        <v>2.5384</v>
       </c>
       <c r="H2" t="n">
-        <v>8.4613</v>
+        <v>7.7514</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3995</v>
+        <v>4.1857</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4424</v>
+        <v>2.5384</v>
       </c>
       <c r="K2" t="n">
         <v>153</v>
@@ -529,7 +529,7 @@
         <v>134</v>
       </c>
       <c r="M2" t="n">
-        <v>6.8419</v>
+        <v>6.7241</v>
       </c>
       <c r="N2" t="n">
         <v>287</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.9932</v>
+        <v>5.0485</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1543</v>
+        <v>1.1671</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6162</v>
+        <v>1.674</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9932</v>
+        <v>5.0485</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3308</v>
+        <v>2.2772</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6624</v>
+        <v>2.7713</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7258</v>
+        <v>2.6193</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4173</v>
+        <v>1.4144</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6624</v>
+        <v>2.7713</v>
       </c>
       <c r="K3" t="n">
         <v>153</v>
@@ -575,7 +575,7 @@
         <v>134</v>
       </c>
       <c r="M3" t="n">
-        <v>4.0797</v>
+        <v>4.185700000000001</v>
       </c>
       <c r="N3" t="n">
         <v>287</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.942</v>
+        <v>4.9945</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1425</v>
+        <v>1.1546</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5931</v>
+        <v>1.6494</v>
       </c>
       <c r="E4" t="n">
-        <v>4.942</v>
+        <v>4.9945</v>
       </c>
       <c r="F4" t="n">
-        <v>2.705</v>
+        <v>2.6667</v>
       </c>
       <c r="G4" t="n">
-        <v>2.237</v>
+        <v>2.3278</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0444</v>
+        <v>3.9041</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1029</v>
+        <v>2.1082</v>
       </c>
       <c r="J4" t="n">
-        <v>2.237</v>
+        <v>2.3278</v>
       </c>
       <c r="K4" t="n">
         <v>153</v>
@@ -621,7 +621,7 @@
         <v>134</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3399</v>
+        <v>4.436</v>
       </c>
       <c r="N4" t="n">
         <v>287</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1623</v>
+        <v>4.1569</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.961</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2411</v>
+        <v>1.2681</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1623</v>
+        <v>4.1569</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9747</v>
+        <v>2.877</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1876</v>
+        <v>1.2799</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9947</v>
+        <v>4.598</v>
       </c>
       <c r="I5" t="n">
-        <v>2.597</v>
+        <v>2.4829</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1876</v>
+        <v>1.2799</v>
       </c>
       <c r="K5" t="n">
         <v>153</v>
@@ -667,7 +667,7 @@
         <v>134</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7846</v>
+        <v>3.7628</v>
       </c>
       <c r="N5" t="n">
         <v>287</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.742</v>
+        <v>3.7603</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8651</v>
+        <v>0.8693</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0513</v>
+        <v>1.0876</v>
       </c>
       <c r="E6" t="n">
-        <v>3.742</v>
+        <v>3.7603</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8146</v>
+        <v>2.7367</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9274</v>
+        <v>1.0236</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4306</v>
+        <v>4.1351</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3037</v>
+        <v>2.2329</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9274</v>
+        <v>1.0236</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -713,7 +713,7 @@
         <v>84</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2311</v>
+        <v>3.2565</v>
       </c>
       <c r="N6" t="n">
         <v>134</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2561</v>
+        <v>3.2758</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7527</v>
+        <v>0.7573</v>
       </c>
       <c r="D7" t="n">
-        <v>0.832</v>
+        <v>0.867</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2561</v>
+        <v>3.2758</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4166</v>
+        <v>2.3482</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8395</v>
+        <v>0.9276</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0282</v>
+        <v>2.8534</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5745</v>
+        <v>1.5408</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8395</v>
+        <v>0.9276</v>
       </c>
       <c r="K7" t="n">
         <v>50</v>
@@ -759,7 +759,7 @@
         <v>84</v>
       </c>
       <c r="M7" t="n">
-        <v>2.414</v>
+        <v>2.4684</v>
       </c>
       <c r="N7" t="n">
         <v>134</v>
@@ -768,185 +768,185 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9756</v>
+        <v>3.0758</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6879</v>
+        <v>0.7111</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7053</v>
+        <v>0.776</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9756</v>
+        <v>3.0758</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3173</v>
+        <v>1.3393</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6583</v>
+        <v>1.7365</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6783</v>
+        <v>1.3393</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3926</v>
+        <v>0.7232</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6583</v>
+        <v>1.7365</v>
       </c>
       <c r="K8" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M8" t="n">
-        <v>2.0509</v>
+        <v>2.4597</v>
       </c>
       <c r="N8" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9386</v>
+        <v>2.9043</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6793</v>
+        <v>0.6714</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6886</v>
+        <v>0.6979</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9386</v>
+        <v>2.9043</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3919</v>
+        <v>2.2358</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5467</v>
+        <v>0.6685</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3919</v>
+        <v>2.4826</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7237</v>
+        <v>1.3406</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5467</v>
+        <v>0.6685</v>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L9" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2704</v>
+        <v>2.0091</v>
       </c>
       <c r="N9" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>znajder</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9336</v>
+        <v>2.8768</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6782</v>
+        <v>0.6651</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6864</v>
+        <v>0.6854</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9336</v>
+        <v>2.8768</v>
       </c>
       <c r="F10" t="n">
-        <v>2.178</v>
+        <v>3.0027</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7556</v>
+        <v>-0.1259</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1877</v>
+        <v>5.0129</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1375</v>
+        <v>2.7069</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7556</v>
+        <v>-0.1259</v>
       </c>
       <c r="K10" t="n">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="L10" t="n">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8931</v>
+        <v>2.581</v>
       </c>
       <c r="N10" t="n">
-        <v>247</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>znajder</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.865</v>
+        <v>2.7772</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6623</v>
+        <v>0.642</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6554</v>
+        <v>0.64</v>
       </c>
       <c r="E11" t="n">
-        <v>2.865</v>
+        <v>2.7772</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0444</v>
+        <v>1.9947</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1794</v>
+        <v>0.7825</v>
       </c>
       <c r="H11" t="n">
-        <v>5.2402</v>
+        <v>1.9947</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7247</v>
+        <v>1.0771</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1794</v>
+        <v>0.7825</v>
       </c>
       <c r="K11" t="n">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="L11" t="n">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5453</v>
+        <v>1.8596</v>
       </c>
       <c r="N11" t="n">
-        <v>126</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5493</v>
+        <v>2.4769</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5893</v>
+        <v>0.5726</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5129</v>
+        <v>0.5033</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5493</v>
+        <v>2.4769</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2815</v>
+        <v>3.1844</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7322</v>
+        <v>-0.7075</v>
       </c>
       <c r="H12" t="n">
-        <v>6.0757</v>
+        <v>5.6125</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1591</v>
+        <v>3.0307</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7322</v>
+        <v>-0.7075</v>
       </c>
       <c r="K12" t="n">
         <v>108</v>
@@ -989,7 +989,7 @@
         <v>139</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4269</v>
+        <v>2.3232</v>
       </c>
       <c r="N12" t="n">
         <v>247</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4838</v>
+        <v>2.4119</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5742</v>
+        <v>0.5576</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4833</v>
+        <v>0.4737</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4838</v>
+        <v>2.4119</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3197</v>
+        <v>2.2157</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1641</v>
+        <v>0.1962</v>
       </c>
       <c r="H13" t="n">
-        <v>2.687</v>
+        <v>2.4163</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3971</v>
+        <v>1.3048</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1641</v>
+        <v>0.1962</v>
       </c>
       <c r="K13" t="n">
         <v>108</v>
@@ -1035,7 +1035,7 @@
         <v>139</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5612</v>
+        <v>1.501</v>
       </c>
       <c r="N13" t="n">
         <v>247</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3188</v>
+        <v>2.2653</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5361</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4088</v>
+        <v>0.407</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3188</v>
+        <v>2.2653</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3047</v>
+        <v>2.2244</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0141</v>
+        <v>0.0409</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6339</v>
+        <v>2.4449</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3695</v>
+        <v>1.3202</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0141</v>
+        <v>0.0409</v>
       </c>
       <c r="K14" t="n">
         <v>50</v>
@@ -1081,7 +1081,7 @@
         <v>84</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3836</v>
+        <v>1.3611</v>
       </c>
       <c r="N14" t="n">
         <v>134</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9929</v>
+        <v>1.8617</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4607</v>
+        <v>0.4304</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2617</v>
+        <v>0.2233</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9929</v>
+        <v>1.8617</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5239</v>
+        <v>2.4317</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.531</v>
+        <v>-0.57</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4065</v>
+        <v>3.1288</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7712</v>
+        <v>1.6895</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.531</v>
+        <v>-0.57</v>
       </c>
       <c r="K15" t="n">
         <v>47</v>
@@ -1127,7 +1127,7 @@
         <v>79</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2402</v>
+        <v>1.1195</v>
       </c>
       <c r="N15" t="n">
         <v>126</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4188</v>
+        <v>1.3208</v>
       </c>
       <c r="C16" t="n">
-        <v>0.328</v>
+        <v>0.3053</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0025</v>
+        <v>-0.0229</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4188</v>
+        <v>1.3208</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4188</v>
+        <v>1.3208</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4188</v>
+        <v>1.3208</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4188</v>
+        <v>1.3208</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4188</v>
+        <v>1.3208</v>
       </c>
       <c r="N16" t="n">
         <v>139</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4048</v>
+        <v>1.3192</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3248</v>
+        <v>0.305</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0038</v>
+        <v>-0.0237</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4048</v>
+        <v>1.3192</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4048</v>
+        <v>1.3192</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4048</v>
+        <v>1.3192</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4048</v>
+        <v>1.3192</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4048</v>
+        <v>1.3192</v>
       </c>
       <c r="N17" t="n">
         <v>128</v>
@@ -1228,185 +1228,185 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>freddieb</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2304</v>
+        <v>1.1951</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2844</v>
+        <v>0.2763</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0825</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2304</v>
+        <v>1.1951</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2304</v>
+        <v>1.1951</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2304</v>
+        <v>1.1951</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2304</v>
+        <v>1.1951</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2304</v>
+        <v>1.1951</v>
       </c>
       <c r="N18" t="n">
-        <v>78</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>freddieb</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2274</v>
+        <v>1.149</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2838</v>
+        <v>0.2656</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0839</v>
+        <v>-0.1012</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2274</v>
+        <v>1.149</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2274</v>
+        <v>1.149</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2274</v>
+        <v>1.149</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2274</v>
+        <v>1.149</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2274</v>
+        <v>1.149</v>
       </c>
       <c r="N19" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7435</v>
+        <v>0.6913</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1719</v>
+        <v>0.1598</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3024</v>
+        <v>-0.3095</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7435</v>
+        <v>0.6913</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7435</v>
+        <v>1.6913</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7435</v>
+        <v>1.6913</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7435</v>
+        <v>0.9133</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K20" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7435</v>
+        <v>-0.0867</v>
       </c>
       <c r="N20" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7411</v>
+        <v>0.6846</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1713</v>
+        <v>0.1583</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3034</v>
+        <v>-0.3126</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7411</v>
+        <v>0.6846</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7411</v>
+        <v>0.6846</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7411</v>
+        <v>0.6846</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9053</v>
+        <v>0.6846</v>
       </c>
       <c r="J21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="L21" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.6846</v>
       </c>
       <c r="N21" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7119</v>
+        <v>0.6523</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1646</v>
+        <v>0.1508</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3166</v>
+        <v>-0.3273</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7119</v>
+        <v>0.6523</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7119</v>
+        <v>0.6523</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7119</v>
+        <v>0.6523</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7119</v>
+        <v>0.6523</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7119</v>
+        <v>0.6523</v>
       </c>
       <c r="N22" t="n">
         <v>139</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6139</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1579</v>
+        <v>0.1419</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3297</v>
+        <v>-0.3447</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6139</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6139</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6139</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6139</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6139</v>
       </c>
       <c r="N23" t="n">
         <v>75</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3976</v>
+        <v>0.3617</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0919</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4585</v>
+        <v>-0.4595</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3976</v>
+        <v>0.3617</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3976</v>
+        <v>0.3617</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3976</v>
+        <v>0.3617</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3976</v>
+        <v>0.3617</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3976</v>
+        <v>0.3617</v>
       </c>
       <c r="N24" t="n">
         <v>78</v>
@@ -1550,35 +1550,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pauf</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2568</v>
+        <v>0.2784</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0594</v>
+        <v>0.0644</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5221</v>
+        <v>-0.4975</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2568</v>
+        <v>0.2784</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4541</v>
+        <v>0.2428</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1973</v>
+        <v>0.0356</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4541</v>
+        <v>0.2428</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2361</v>
+        <v>0.1311</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1973</v>
+        <v>0.0356</v>
       </c>
       <c r="K25" t="n">
         <v>47</v>
@@ -1587,7 +1587,7 @@
         <v>79</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0388</v>
+        <v>0.1667</v>
       </c>
       <c r="N25" t="n">
         <v>126</v>
@@ -1596,35 +1596,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>pauf</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2093</v>
+        <v>0.2454</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0484</v>
+        <v>0.0567</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5435</v>
+        <v>-0.5125</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2093</v>
+        <v>0.2454</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2069</v>
+        <v>0.4426</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0024</v>
+        <v>-0.1972</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2069</v>
+        <v>0.4426</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1076</v>
+        <v>0.239</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0024</v>
+        <v>-0.1972</v>
       </c>
       <c r="K26" t="n">
         <v>47</v>
@@ -1633,7 +1633,7 @@
         <v>79</v>
       </c>
       <c r="M26" t="n">
-        <v>0.11</v>
+        <v>0.0418</v>
       </c>
       <c r="N26" t="n">
         <v>126</v>
@@ -1642,139 +1642,139 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0484</v>
+        <v>-0.0076</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0112</v>
+        <v>-0.0018</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6599</v>
+        <v>-0.6277</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0484</v>
+        <v>-0.0076</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0484</v>
+        <v>-0.0076</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0484</v>
+        <v>-0.0076</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0484</v>
+        <v>-0.0076</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0484</v>
+        <v>-0.0076</v>
       </c>
       <c r="N27" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0488</v>
+        <v>-0.0713</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0113</v>
+        <v>-0.0165</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.66</v>
+        <v>-0.6567</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0488</v>
+        <v>-0.0713</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0488</v>
+        <v>-0.0713</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0488</v>
+        <v>-0.0713</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0488</v>
+        <v>-0.0713</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0488</v>
+        <v>-0.0713</v>
       </c>
       <c r="N28" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1468</v>
+        <v>-0.1018</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0339</v>
+        <v>-0.0235</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7043</v>
+        <v>-0.6705</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1468</v>
+        <v>-0.1018</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1468</v>
+        <v>-2.2221</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2.1203</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1468</v>
+        <v>-2.2221</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1468</v>
+        <v>-1.1999</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2.1203</v>
       </c>
       <c r="K29" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1468</v>
+        <v>0.9203999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>128</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1655</v>
+        <v>-0.1924</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0383</v>
+        <v>-0.0445</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7127</v>
+        <v>-0.7118</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1655</v>
+        <v>-0.1924</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1655</v>
+        <v>-0.1924</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1655</v>
+        <v>-0.1924</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1655</v>
+        <v>-0.1924</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1655</v>
+        <v>-0.1924</v>
       </c>
       <c r="N30" t="n">
         <v>139</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1919</v>
+        <v>-0.2015</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0444</v>
+        <v>-0.0466</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7246</v>
+        <v>-0.7159</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1919</v>
+        <v>-0.2015</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1919</v>
+        <v>-0.2015</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1919</v>
+        <v>-0.2015</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1919</v>
+        <v>-0.2015</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1919</v>
+        <v>-0.2015</v>
       </c>
       <c r="N31" t="n">
         <v>128</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3798</v>
+        <v>-0.2237</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0878</v>
+        <v>-0.0517</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8095</v>
+        <v>-0.726</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3798</v>
+        <v>-0.2237</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.3775</v>
+        <v>-0.2237</v>
       </c>
       <c r="G32" t="n">
-        <v>1.9977</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-2.3775</v>
+        <v>-0.2237</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.2362</v>
+        <v>-0.2237</v>
       </c>
       <c r="J32" t="n">
-        <v>1.9977</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="L32" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7615000000000001</v>
+        <v>-0.2237</v>
       </c>
       <c r="N32" t="n">
-        <v>287</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3927</v>
+        <v>-0.429</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0992</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8153</v>
+        <v>-0.8195</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3927</v>
+        <v>-0.429</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3927</v>
+        <v>-0.429</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3927</v>
+        <v>-0.429</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3927</v>
+        <v>-0.429</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3927</v>
+        <v>-0.429</v>
       </c>
       <c r="N33" t="n">
         <v>75</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3958</v>
+        <v>-0.4353</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0915</v>
+        <v>-0.1006</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8167</v>
+        <v>-0.8224</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3958</v>
+        <v>-0.4353</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3958</v>
+        <v>-0.4353</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3958</v>
+        <v>-0.4353</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3958</v>
+        <v>-0.4353</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3958</v>
+        <v>-0.4353</v>
       </c>
       <c r="N34" t="n">
         <v>78</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.421</v>
+        <v>-0.4976</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0973</v>
+        <v>-0.115</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.8507</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.421</v>
+        <v>-0.4976</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1823</v>
+        <v>-0.2406</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2387</v>
+        <v>-0.257</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.1823</v>
+        <v>-0.2406</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0948</v>
+        <v>-0.1299</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2387</v>
+        <v>-0.257</v>
       </c>
       <c r="K35" t="n">
         <v>108</v>
@@ -2047,7 +2047,7 @@
         <v>139</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3335</v>
+        <v>-0.3869</v>
       </c>
       <c r="N35" t="n">
         <v>247</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6857</v>
+        <v>-0.7389</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1585</v>
+        <v>-0.1708</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9476</v>
+        <v>-0.9606</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6857</v>
+        <v>-0.7389</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6857</v>
+        <v>-0.7389</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6857</v>
+        <v>-0.7389</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6857</v>
+        <v>-0.7389</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6857</v>
+        <v>-0.7389</v>
       </c>
       <c r="N36" t="n">
         <v>75</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7397</v>
+        <v>-0.7784</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.171</v>
+        <v>-0.18</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.972</v>
+        <v>-0.9785</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7397</v>
+        <v>-0.7784</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7397</v>
+        <v>-0.7784</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7397</v>
+        <v>-0.7784</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7397</v>
+        <v>-0.7784</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7397</v>
+        <v>-0.7784</v>
       </c>
       <c r="N37" t="n">
         <v>75</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7941</v>
+        <v>-0.8337</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1836</v>
+        <v>-0.1927</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9965000000000001</v>
+        <v>-1.0037</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7941</v>
+        <v>-0.8337</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7941</v>
+        <v>-0.8337</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7941</v>
+        <v>-0.8337</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7941</v>
+        <v>-0.8337</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7941</v>
+        <v>-0.8337</v>
       </c>
       <c r="N38" t="n">
         <v>75</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.8993</v>
+        <v>-0.9349</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2079</v>
+        <v>-0.2161</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.044</v>
+        <v>-1.0498</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.8993</v>
+        <v>-0.9349</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.8993</v>
+        <v>-0.9349</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8993</v>
+        <v>-0.9349</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8993</v>
+        <v>-0.9349</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.8993</v>
+        <v>-0.9349</v>
       </c>
       <c r="N39" t="n">
         <v>78</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.0493</v>
+        <v>-1.0479</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2426</v>
+        <v>-0.2423</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1117</v>
+        <v>-1.1012</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.0493</v>
+        <v>-1.0479</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.0493</v>
+        <v>-1.0479</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.0493</v>
+        <v>-1.0479</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.0493</v>
+        <v>-1.0479</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.0493</v>
+        <v>-1.0479</v>
       </c>
       <c r="N40" t="n">
         <v>139</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.0752</v>
+        <v>-1.8959</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4797</v>
+        <v>-0.4383</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5749</v>
+        <v>-1.4873</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.0752</v>
+        <v>-1.8959</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.2712</v>
+        <v>-2.1178</v>
       </c>
       <c r="G41" t="n">
-        <v>0.196</v>
+        <v>0.2219</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.2712</v>
+        <v>-2.1178</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.1809</v>
+        <v>-1.1436</v>
       </c>
       <c r="J41" t="n">
-        <v>0.196</v>
+        <v>0.2219</v>
       </c>
       <c r="K41" t="n">
         <v>108</v>
@@ -2323,7 +2323,7 @@
         <v>139</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.9849000000000001</v>
+        <v>-0.9217</v>
       </c>
       <c r="N41" t="n">
         <v>247</v>
@@ -2429,10 +2429,10 @@
         <v>1.65</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3171</v>
+        <v>1.3957</v>
       </c>
       <c r="J2" t="n">
-        <v>34.2446</v>
+        <v>36.2882</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.25</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6446</v>
       </c>
       <c r="J3" t="n">
-        <v>17.3914</v>
+        <v>16.7596</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6236</v>
+        <v>0.6039</v>
       </c>
       <c r="J4" t="n">
-        <v>16.2136</v>
+        <v>15.7014</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2912</v>
+        <v>0.3024</v>
       </c>
       <c r="J5" t="n">
-        <v>7.5712</v>
+        <v>7.8624</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0056</v>
+        <v>0.018</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1456</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1827</v>
+        <v>0.1794</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7502</v>
+        <v>4.6644</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0354</v>
+        <v>0.0256</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9204</v>
+        <v>0.6656</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2113</v>
+        <v>-0.2288</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.4938</v>
+        <v>-5.9488</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.71</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3085</v>
+        <v>-0.3242</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.021000000000001</v>
+        <v>-8.4292</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3181</v>
+        <v>-0.3334</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.2706</v>
+        <v>-8.6684</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0258</v>
+        <v>0.9778</v>
       </c>
       <c r="J12" t="n">
-        <v>29.7482</v>
+        <v>28.3562</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8495</v>
+        <v>0.8044</v>
       </c>
       <c r="J13" t="n">
-        <v>24.6355</v>
+        <v>23.3276</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.22</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6005</v>
+        <v>0.5831</v>
       </c>
       <c r="J14" t="n">
-        <v>17.4145</v>
+        <v>16.9099</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4529</v>
+        <v>0.4502</v>
       </c>
       <c r="J15" t="n">
-        <v>13.1341</v>
+        <v>13.0558</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2917</v>
+        <v>0.3027</v>
       </c>
       <c r="J16" t="n">
-        <v>8.459300000000001</v>
+        <v>8.7783</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.11</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3191</v>
+        <v>0.3103</v>
       </c>
       <c r="J17" t="n">
-        <v>9.2539</v>
+        <v>8.998699999999999</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.88</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.141</v>
+        <v>-0.1577</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.089</v>
+        <v>-4.5733</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1813</v>
+        <v>-0.1987</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.2577</v>
+        <v>-5.7623</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.74</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2792</v>
+        <v>-0.2957</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.0968</v>
+        <v>-8.5753</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.68</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3365</v>
+        <v>-0.3514</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.7585</v>
+        <v>-10.1906</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.35</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5581</v>
+        <v>0.6197</v>
       </c>
       <c r="J22" t="n">
-        <v>15.6268</v>
+        <v>17.3516</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3677</v>
+        <v>0.3878</v>
       </c>
       <c r="J23" t="n">
-        <v>10.2956</v>
+        <v>10.8584</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.042</v>
+        <v>0.0464</v>
       </c>
       <c r="J24" t="n">
-        <v>1.176</v>
+        <v>1.2992</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.71</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3237</v>
+        <v>-0.3361</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.063599999999999</v>
+        <v>-9.4108</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.63</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3989</v>
+        <v>-0.4086</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.1692</v>
+        <v>-11.4408</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.35</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6825</v>
+        <v>0.7542</v>
       </c>
       <c r="J27" t="n">
-        <v>19.11</v>
+        <v>21.1176</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.25</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5444</v>
+        <v>0.6021</v>
       </c>
       <c r="J28" t="n">
-        <v>15.2432</v>
+        <v>16.8588</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5017</v>
+        <v>0.5546</v>
       </c>
       <c r="J29" t="n">
-        <v>14.0476</v>
+        <v>15.5288</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.97</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1686</v>
+        <v>-0.1622</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.7208</v>
+        <v>-4.5416</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.95</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.237</v>
+        <v>-0.2279</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.636</v>
+        <v>-6.3812</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.57</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5374</v>
+        <v>0.6172</v>
       </c>
       <c r="J32" t="n">
-        <v>13.9724</v>
+        <v>16.0472</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.53</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>13.3276</v>
+        <v>15.2932</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.5</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4939</v>
+        <v>0.5662</v>
       </c>
       <c r="J34" t="n">
-        <v>12.8414</v>
+        <v>14.7212</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.98</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.065</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.69</v>
+        <v>-1.6952</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.92</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1417</v>
+        <v>-0.1471</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.6842</v>
+        <v>-3.8246</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.96</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0353</v>
+        <v>-0.0509</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-1.3234</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.85</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1651</v>
+        <v>-0.1839</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.2926</v>
+        <v>-4.7814</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.77</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2431</v>
+        <v>-0.2619</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.3206</v>
+        <v>-6.8094</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.77</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2431</v>
+        <v>-0.2619</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.3206</v>
+        <v>-6.8094</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.62</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3851</v>
+        <v>-0.3994</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.0126</v>
+        <v>-10.3844</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.476</v>
+        <v>0.5286</v>
       </c>
       <c r="J42" t="n">
-        <v>14.28</v>
+        <v>15.858</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.21</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4028</v>
+        <v>0.4422</v>
       </c>
       <c r="J43" t="n">
-        <v>12.084</v>
+        <v>13.266</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.16</v>
       </c>
       <c r="I44" t="n">
-        <v>0.348</v>
+        <v>0.36</v>
       </c>
       <c r="J44" t="n">
-        <v>10.44</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0221</v>
+        <v>-0.0264</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.663</v>
+        <v>-0.792</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.46</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5565</v>
+        <v>-0.5577</v>
       </c>
       <c r="J46" t="n">
-        <v>-16.695</v>
+        <v>-16.731</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.4</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.8368</v>
       </c>
       <c r="J47" t="n">
-        <v>22.818</v>
+        <v>25.104</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.11</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3417</v>
+        <v>0.3486</v>
       </c>
       <c r="J48" t="n">
-        <v>10.251</v>
+        <v>10.458</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.08</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2663</v>
+        <v>0.2715</v>
       </c>
       <c r="J49" t="n">
-        <v>7.989</v>
+        <v>8.145</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1425</v>
+        <v>0.1539</v>
       </c>
       <c r="J50" t="n">
-        <v>4.275</v>
+        <v>4.617</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.9</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3789</v>
+        <v>-0.3629</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.367</v>
+        <v>-10.887</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3632</v>
+        <v>0.3705</v>
       </c>
       <c r="J52" t="n">
-        <v>9.8064</v>
+        <v>10.0035</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.1115</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.5839</v>
+        <v>-3.0105</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.8</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2202</v>
+        <v>-0.2378</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.9454</v>
+        <v>-6.4206</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3265</v>
+        <v>-0.3418</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.8155</v>
+        <v>-9.2286</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.336</v>
+        <v>-0.351</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.071999999999999</v>
+        <v>-9.477</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.53</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8812</v>
+        <v>0.9761</v>
       </c>
       <c r="J57" t="n">
-        <v>23.7924</v>
+        <v>26.3547</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.35</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6551</v>
+        <v>0.7304</v>
       </c>
       <c r="J58" t="n">
-        <v>17.6877</v>
+        <v>19.7208</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.24</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5115</v>
+        <v>0.5703</v>
       </c>
       <c r="J59" t="n">
-        <v>13.8105</v>
+        <v>15.3981</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.23</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4975</v>
+        <v>0.5547</v>
       </c>
       <c r="J60" t="n">
-        <v>13.4325</v>
+        <v>14.9769</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.21</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4692</v>
+        <v>0.5229</v>
       </c>
       <c r="J61" t="n">
-        <v>12.6684</v>
+        <v>14.1183</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.6</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5552</v>
+        <v>0.6381</v>
       </c>
       <c r="J62" t="n">
-        <v>15.5456</v>
+        <v>17.8668</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.48</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4808</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>13.4624</v>
+        <v>15.4252</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.29</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3596</v>
+        <v>0.3945</v>
       </c>
       <c r="J64" t="n">
-        <v>10.0688</v>
+        <v>11.046</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.23</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3079</v>
+        <v>0.3273</v>
       </c>
       <c r="J65" t="n">
-        <v>8.6212</v>
+        <v>9.164400000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1305</v>
+        <v>-0.1353</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.654</v>
+        <v>-3.7884</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>0.237</v>
+        <v>0.2304</v>
       </c>
       <c r="J67" t="n">
-        <v>6.636</v>
+        <v>6.4512</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.86</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1525</v>
+        <v>-0.1718</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.27</v>
+        <v>-4.8104</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.72</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.289</v>
+        <v>-0.3072</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.092000000000001</v>
+        <v>-8.601599999999999</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.63</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.374</v>
+        <v>-0.3891</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.472</v>
+        <v>-10.8948</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.61</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3927</v>
+        <v>-0.407</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.9956</v>
+        <v>-11.396</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.97</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.0128</v>
+        <v>-0.0293</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.3072</v>
+        <v>-0.7032</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.79</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2209</v>
+        <v>-0.2407</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.3016</v>
+        <v>-5.7768</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.75</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2582</v>
+        <v>-0.2775</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.1968</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3048</v>
+        <v>-0.3232</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.3152</v>
+        <v>-7.7568</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.59</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4081</v>
+        <v>-0.4222</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.7944</v>
+        <v>-10.1328</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8428</v>
+        <v>0.9325</v>
       </c>
       <c r="J77" t="n">
-        <v>20.2272</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.48</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>19.9224</v>
+        <v>22.0536</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4902</v>
+        <v>0.5448</v>
       </c>
       <c r="J79" t="n">
-        <v>11.7648</v>
+        <v>13.0752</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.06</v>
       </c>
       <c r="I80" t="n">
-        <v>0.171</v>
+        <v>0.1906</v>
       </c>
       <c r="J80" t="n">
-        <v>4.104</v>
+        <v>4.5744</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.02</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0341</v>
+        <v>0.0584</v>
       </c>
       <c r="J81" t="n">
-        <v>0.8184</v>
+        <v>1.4016</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.45</v>
       </c>
       <c r="I82" t="n">
-        <v>1.094</v>
+        <v>1.0488</v>
       </c>
       <c r="J82" t="n">
-        <v>31.726</v>
+        <v>30.4152</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.38</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9905</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>28.7245</v>
+        <v>26.9381</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.03</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1015</v>
+        <v>0.116</v>
       </c>
       <c r="J84" t="n">
-        <v>2.9435</v>
+        <v>3.364</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.98</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1272</v>
+        <v>-0.1226</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.6888</v>
+        <v>-3.5554</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.606</v>
+        <v>-0.5669</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.574</v>
+        <v>-16.4401</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.13</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3108</v>
+        <v>0.3129</v>
       </c>
       <c r="J87" t="n">
-        <v>9.013199999999999</v>
+        <v>9.0741</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.01</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0402</v>
+        <v>0.0451</v>
       </c>
       <c r="J88" t="n">
-        <v>1.1658</v>
+        <v>1.3079</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0487</v>
+        <v>-0.0572</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.4123</v>
+        <v>-1.6588</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0849</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.1576</v>
+        <v>-2.4621</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1756</v>
+        <v>-0.1895</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.0924</v>
+        <v>-5.4955</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.27</v>
       </c>
       <c r="I92" t="n">
-        <v>0.759</v>
+        <v>0.716</v>
       </c>
       <c r="J92" t="n">
-        <v>22.77</v>
+        <v>21.48</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6611</v>
+        <v>0.6297</v>
       </c>
       <c r="J93" t="n">
-        <v>19.833</v>
+        <v>18.891</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3786</v>
+        <v>0.3753</v>
       </c>
       <c r="J94" t="n">
-        <v>11.358</v>
+        <v>11.259</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.97</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1532</v>
+        <v>-0.1515</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.596</v>
+        <v>-4.545</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.86</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4872</v>
+        <v>-0.4624</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.616</v>
+        <v>-13.872</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.31</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6284</v>
+        <v>0.6087</v>
       </c>
       <c r="J97" t="n">
-        <v>18.852</v>
+        <v>18.261</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2014</v>
+        <v>0.2099</v>
       </c>
       <c r="J98" t="n">
-        <v>6.042</v>
+        <v>6.297</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.001</v>
+        <v>-0.0007</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.03</v>
+        <v>-0.021</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.86</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1793</v>
+        <v>-0.1923</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.379</v>
+        <v>-5.769</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.83</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2105</v>
+        <v>-0.2236</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.315</v>
+        <v>-6.708</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.78</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8952</v>
+        <v>0.8793</v>
       </c>
       <c r="J102" t="n">
-        <v>19.6944</v>
+        <v>19.3446</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.44</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5506</v>
       </c>
       <c r="J103" t="n">
-        <v>11.8976</v>
+        <v>12.1132</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.33</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4212</v>
+        <v>0.4368</v>
       </c>
       <c r="J104" t="n">
-        <v>9.266400000000001</v>
+        <v>9.6096</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.13</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1818</v>
+        <v>0.2028</v>
       </c>
       <c r="J105" t="n">
-        <v>3.9996</v>
+        <v>4.4616</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2385</v>
+        <v>-0.2457</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.247</v>
+        <v>-5.4054</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.02</v>
       </c>
       <c r="I107" t="n">
-        <v>0.0793</v>
+        <v>0.0788</v>
       </c>
       <c r="J107" t="n">
-        <v>1.7446</v>
+        <v>1.7336</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.97</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.034</v>
+        <v>-0.0459</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.748</v>
+        <v>-1.0098</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1623</v>
+        <v>-0.1793</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.5706</v>
+        <v>-3.9446</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.84</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.182</v>
+        <v>-0.1993</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.004</v>
+        <v>-4.3846</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.6</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4127</v>
+        <v>-0.4242</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.0794</v>
+        <v>-9.3324</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.15</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4059</v>
+        <v>0.391</v>
       </c>
       <c r="J112" t="n">
-        <v>10.1475</v>
+        <v>9.775</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.9</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1181</v>
+        <v>-0.1346</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.9525</v>
+        <v>-3.365</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.76</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2587</v>
+        <v>-0.276</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.4675</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2781</v>
+        <v>-0.2949</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.9525</v>
+        <v>-7.3725</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.66</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3544</v>
+        <v>-0.3687</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.859999999999999</v>
+        <v>-9.217499999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.73</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4113</v>
+        <v>1.3941</v>
       </c>
       <c r="J117" t="n">
-        <v>35.2825</v>
+        <v>34.8525</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.55</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1905</v>
+        <v>1.1595</v>
       </c>
       <c r="J118" t="n">
-        <v>29.7625</v>
+        <v>28.9875</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.29</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7568</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>18.92</v>
+        <v>18.0825</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2973</v>
+        <v>-0.2781</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.4325</v>
+        <v>-6.9525</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7145</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="J121" t="n">
-        <v>-17.8625</v>
+        <v>-16.445</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.08</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2512</v>
+        <v>0.2462</v>
       </c>
       <c r="J122" t="n">
-        <v>6.0288</v>
+        <v>5.9088</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.95</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0606</v>
+        <v>-0.0743</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.4544</v>
+        <v>-1.7832</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.82</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2016</v>
+        <v>-0.2191</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.8384</v>
+        <v>-5.2584</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2115</v>
+        <v>-0.2289</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.076</v>
+        <v>-5.4936</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.62</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3938</v>
+        <v>-0.4062</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.4512</v>
+        <v>-9.748799999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.42</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0464</v>
+        <v>0.9938</v>
       </c>
       <c r="J127" t="n">
-        <v>25.1136</v>
+        <v>23.8512</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6637</v>
+        <v>0.6362</v>
       </c>
       <c r="J128" t="n">
-        <v>15.9288</v>
+        <v>15.2688</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.17</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4936</v>
+        <v>0.4835</v>
       </c>
       <c r="J129" t="n">
-        <v>11.8464</v>
+        <v>11.604</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.14</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4191</v>
+        <v>0.4154</v>
       </c>
       <c r="J130" t="n">
-        <v>10.0584</v>
+        <v>9.9696</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.83</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5868</v>
+        <v>-0.5484</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.0832</v>
+        <v>-13.1616</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.42</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0501</v>
+        <v>0.9974</v>
       </c>
       <c r="J132" t="n">
-        <v>27.3026</v>
+        <v>25.9324</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.21</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5948</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>15.4648</v>
+        <v>14.9266</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4214</v>
+        <v>0.4169</v>
       </c>
       <c r="J134" t="n">
-        <v>10.9564</v>
+        <v>10.8394</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.14</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4214</v>
+        <v>0.4169</v>
       </c>
       <c r="J135" t="n">
-        <v>10.9564</v>
+        <v>10.8394</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.82</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6096</v>
+        <v>-0.5695</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.8496</v>
+        <v>-14.807</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.35</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.6953</v>
       </c>
       <c r="J137" t="n">
-        <v>18.9878</v>
+        <v>18.0778</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0829</v>
+        <v>-0.095</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.1554</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1386</v>
+        <v>-0.1531</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.6036</v>
+        <v>-3.9806</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.16</v>
+        <v>-0.1749</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.16</v>
+        <v>-4.5474</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.65</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3763</v>
+        <v>-0.3876</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.783799999999999</v>
+        <v>-10.0776</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.26</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7598</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>22.0342</v>
+        <v>20.6538</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.03</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1242</v>
+        <v>0.1315</v>
       </c>
       <c r="J143" t="n">
-        <v>3.6018</v>
+        <v>3.8135</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0056</v>
+        <v>-0.0038</v>
       </c>
       <c r="J144" t="n">
-        <v>-0.1624</v>
+        <v>-0.1102</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.97</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1374</v>
+        <v>-0.1405</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.9846</v>
+        <v>-4.0745</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.89</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3862</v>
+        <v>-0.3743</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.1998</v>
+        <v>-10.8547</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.39</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7484</v>
+        <v>0.7195</v>
       </c>
       <c r="J147" t="n">
-        <v>21.7036</v>
+        <v>20.8655</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.14</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3118</v>
+        <v>0.3179</v>
       </c>
       <c r="J148" t="n">
-        <v>9.042199999999999</v>
+        <v>9.219099999999999</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1311</v>
+        <v>0.142</v>
       </c>
       <c r="J149" t="n">
-        <v>3.8019</v>
+        <v>4.118</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.97</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0555</v>
+        <v>-0.0624</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.6095</v>
+        <v>-1.8096</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.73</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3138</v>
+        <v>-0.3247</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.100199999999999</v>
+        <v>-9.4163</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.32</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6583</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>19.749</v>
+        <v>19.008</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.97</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0487</v>
+        <v>-0.0572</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.461</v>
+        <v>-1.716</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.93</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0984</v>
+        <v>-0.1102</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.952</v>
+        <v>-3.306</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.87</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.165</v>
+        <v>-0.1788</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.95</v>
+        <v>-5.364</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.83</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2068</v>
+        <v>-0.2207</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.204</v>
+        <v>-6.621</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.35</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8546</v>
       </c>
       <c r="J157" t="n">
-        <v>27.294</v>
+        <v>25.638</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.32</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8418</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>25.254</v>
+        <v>23.847</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.2</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5611</v>
+        <v>0.5458</v>
       </c>
       <c r="J159" t="n">
-        <v>16.833</v>
+        <v>16.374</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.18</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5137</v>
+        <v>0.5028</v>
       </c>
       <c r="J160" t="n">
-        <v>15.411</v>
+        <v>15.084</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.91</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3722</v>
+        <v>-0.3518</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.166</v>
+        <v>-10.554</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.99</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.0034</v>
+        <v>-0.012</v>
       </c>
       <c r="J162" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.276</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.9</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1205</v>
+        <v>-0.1364</v>
       </c>
       <c r="J163" t="n">
-        <v>-2.7715</v>
+        <v>-3.1372</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.88</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1421</v>
+        <v>-0.1585</v>
       </c>
       <c r="J164" t="n">
-        <v>-3.2683</v>
+        <v>-3.6455</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2514</v>
+        <v>-0.2682</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.7822</v>
+        <v>-6.1686</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.76</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2611</v>
+        <v>-0.2778</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.0053</v>
+        <v>-6.3894</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.55</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1914</v>
+        <v>1.1603</v>
       </c>
       <c r="J167" t="n">
-        <v>27.4022</v>
+        <v>26.6869</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.55</v>
       </c>
       <c r="I168" t="n">
-        <v>1.1914</v>
+        <v>1.1603</v>
       </c>
       <c r="J168" t="n">
-        <v>27.4022</v>
+        <v>26.6869</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.13</v>
       </c>
       <c r="I169" t="n">
-        <v>0.372</v>
+        <v>0.377</v>
       </c>
       <c r="J169" t="n">
-        <v>8.555999999999999</v>
+        <v>8.670999999999999</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.08</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2314</v>
+        <v>0.2473</v>
       </c>
       <c r="J170" t="n">
-        <v>5.3222</v>
+        <v>5.6879</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1958</v>
+        <v>-0.1812</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.5034</v>
+        <v>-4.1676</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.07</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2727</v>
+        <v>0.2569</v>
       </c>
       <c r="J172" t="n">
-        <v>6.5448</v>
+        <v>6.1656</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.85</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1604</v>
+        <v>-0.1803</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.8496</v>
+        <v>-4.3272</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2681</v>
+        <v>-0.2872</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.4344</v>
+        <v>-6.8928</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.65</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3528</v>
+        <v>-0.3692</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.4672</v>
+        <v>-8.860799999999999</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.52</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4742</v>
+        <v>-0.4845</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.3808</v>
+        <v>-11.628</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.55</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1762</v>
+        <v>1.1469</v>
       </c>
       <c r="J177" t="n">
-        <v>28.2288</v>
+        <v>27.5256</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.36</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8973</v>
+        <v>0.8498</v>
       </c>
       <c r="J178" t="n">
-        <v>21.5352</v>
+        <v>20.3952</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.29</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7466</v>
+        <v>0.7164</v>
       </c>
       <c r="J179" t="n">
-        <v>17.9184</v>
+        <v>17.1936</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7466</v>
+        <v>0.7164</v>
       </c>
       <c r="J180" t="n">
-        <v>17.9184</v>
+        <v>17.1936</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.16</v>
       </c>
       <c r="I181" t="n">
-        <v>0.4343</v>
+        <v>0.4372</v>
       </c>
       <c r="J181" t="n">
-        <v>10.4232</v>
+        <v>10.4928</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.6</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2654</v>
+        <v>1.2371</v>
       </c>
       <c r="J182" t="n">
-        <v>35.4312</v>
+        <v>34.6388</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.48</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1134</v>
+        <v>1.0744</v>
       </c>
       <c r="J183" t="n">
-        <v>31.1752</v>
+        <v>30.0832</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.18</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5107</v>
+        <v>0.5008</v>
       </c>
       <c r="J184" t="n">
-        <v>14.2996</v>
+        <v>14.0224</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.406</v>
+        <v>-0.3819</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.368</v>
+        <v>-10.6932</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.89</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4347</v>
+        <v>-0.4082</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.1716</v>
+        <v>-11.4296</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.08</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2247</v>
+        <v>0.2268</v>
       </c>
       <c r="J187" t="n">
-        <v>6.2916</v>
+        <v>6.3504</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.98</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0298</v>
+        <v>-0.038</v>
       </c>
       <c r="J188" t="n">
-        <v>-0.8344</v>
+        <v>-1.064</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.98</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0298</v>
+        <v>-0.038</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.8344</v>
+        <v>-1.064</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.92</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1046</v>
+        <v>-0.1182</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.9288</v>
+        <v>-3.3096</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3467</v>
+        <v>-0.3593</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.707599999999999</v>
+        <v>-10.0604</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.27</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6428</v>
+        <v>0.6073</v>
       </c>
       <c r="J192" t="n">
-        <v>14.7844</v>
+        <v>13.9679</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.84</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1803</v>
+        <v>-0.198</v>
       </c>
       <c r="J193" t="n">
-        <v>-4.1469</v>
+        <v>-4.554</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.77</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2483</v>
+        <v>-0.2658</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.7109</v>
+        <v>-6.1134</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.74</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2773</v>
+        <v>-0.2942</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.3779</v>
+        <v>-6.7666</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4469</v>
+        <v>-0.4571</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.2787</v>
+        <v>-10.5133</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.86</v>
       </c>
       <c r="I197" t="n">
-        <v>1.5697</v>
+        <v>1.56</v>
       </c>
       <c r="J197" t="n">
-        <v>36.1031</v>
+        <v>35.88</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.42</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0246</v>
+        <v>0.9731</v>
       </c>
       <c r="J198" t="n">
-        <v>23.5658</v>
+        <v>22.3813</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.24</v>
       </c>
       <c r="I199" t="n">
-        <v>0.646</v>
+        <v>0.6242</v>
       </c>
       <c r="J199" t="n">
-        <v>14.858</v>
+        <v>14.3566</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.93</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3267</v>
+        <v>-0.3061</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.5141</v>
+        <v>-7.0403</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6612</v>
+        <v>-0.6108</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.2076</v>
+        <v>-14.0484</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.32</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6574</v>
+        <v>0.633</v>
       </c>
       <c r="J202" t="n">
-        <v>19.0646</v>
+        <v>18.357</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.05</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1422</v>
+        <v>0.15</v>
       </c>
       <c r="J203" t="n">
-        <v>4.1238</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.04</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1189</v>
+        <v>0.1266</v>
       </c>
       <c r="J204" t="n">
-        <v>3.4481</v>
+        <v>3.6714</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2573</v>
+        <v>-0.2708</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.4617</v>
+        <v>-7.8532</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.74</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2964</v>
+        <v>-0.3091</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.595599999999999</v>
+        <v>-8.963900000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.36</v>
       </c>
       <c r="I207" t="n">
-        <v>0.959</v>
+        <v>0.8955</v>
       </c>
       <c r="J207" t="n">
-        <v>27.811</v>
+        <v>25.9695</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.32</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8697</v>
+        <v>0.8143</v>
       </c>
       <c r="J208" t="n">
-        <v>25.2213</v>
+        <v>23.6147</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.11</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3483</v>
+        <v>0.3482</v>
       </c>
       <c r="J209" t="n">
-        <v>10.1007</v>
+        <v>10.0978</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.02</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0696</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="J210" t="n">
-        <v>2.0184</v>
+        <v>2.4099</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.75</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7804</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="J211" t="n">
-        <v>-22.6316</v>
+        <v>-20.9467</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.5</v>
       </c>
       <c r="I212" t="n">
-        <v>1.1313</v>
+        <v>1.0953</v>
       </c>
       <c r="J212" t="n">
-        <v>28.2825</v>
+        <v>27.3825</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.41</v>
       </c>
       <c r="I213" t="n">
-        <v>1.0108</v>
+        <v>0.9573</v>
       </c>
       <c r="J213" t="n">
-        <v>25.27</v>
+        <v>23.9325</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.34</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8724</v>
+        <v>0.8243</v>
       </c>
       <c r="J214" t="n">
-        <v>21.81</v>
+        <v>20.6075</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.02</v>
       </c>
       <c r="I215" t="n">
-        <v>0.0365</v>
+        <v>0.0601</v>
       </c>
       <c r="J215" t="n">
-        <v>0.9125</v>
+        <v>1.5025</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.95</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2613</v>
+        <v>-0.2449</v>
       </c>
       <c r="J216" t="n">
-        <v>-6.5325</v>
+        <v>-6.1225</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.19</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4913</v>
+        <v>0.4689</v>
       </c>
       <c r="J217" t="n">
-        <v>12.2825</v>
+        <v>11.7225</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.96</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0431</v>
+        <v>-0.0571</v>
       </c>
       <c r="J218" t="n">
-        <v>-1.0775</v>
+        <v>-1.4275</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.76</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2574</v>
+        <v>-0.2749</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.435</v>
+        <v>-6.8725</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.64</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3718</v>
+        <v>-0.3857</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.295</v>
+        <v>-9.6425</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.61</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3999</v>
+        <v>-0.4126</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.9975</v>
+        <v>-10.315</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3113</v>
+        <v>1.2952</v>
       </c>
       <c r="J222" t="n">
-        <v>28.8486</v>
+        <v>28.4944</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.55</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1584</v>
+        <v>1.1314</v>
       </c>
       <c r="J223" t="n">
-        <v>25.4848</v>
+        <v>24.8908</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.45</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0383</v>
+        <v>0.9958</v>
       </c>
       <c r="J224" t="n">
-        <v>22.8426</v>
+        <v>21.9076</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.35</v>
       </c>
       <c r="I225" t="n">
-        <v>0.8588</v>
+        <v>0.8194</v>
       </c>
       <c r="J225" t="n">
-        <v>18.8936</v>
+        <v>18.0268</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.18</v>
       </c>
       <c r="I226" t="n">
-        <v>0.4611</v>
+        <v>0.4664</v>
       </c>
       <c r="J226" t="n">
-        <v>10.1442</v>
+        <v>10.2608</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.05</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2761</v>
+        <v>0.2485</v>
       </c>
       <c r="J227" t="n">
-        <v>6.0742</v>
+        <v>5.467</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.78</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2178</v>
+        <v>-0.2404</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.7916</v>
+        <v>-5.2888</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.65</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3406</v>
+        <v>-0.3598</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.4932</v>
+        <v>-7.9156</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.48</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4992</v>
+        <v>-0.5097</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.9824</v>
+        <v>-11.2134</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.47</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.5185</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.1892</v>
+        <v>-11.407</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2109/event_2109_evp_summary.xlsx
+++ b/database/event/2109/event_2109_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.3711</v>
+        <v>6.1963</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4729</v>
+        <v>1.4325</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2761</v>
+        <v>2.2169</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3711</v>
+        <v>6.1963</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8327</v>
+        <v>3.6649</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5384</v>
+        <v>2.5314</v>
       </c>
       <c r="H2" t="n">
-        <v>7.7514</v>
+        <v>7.3171</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1857</v>
+        <v>4.1083</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5384</v>
+        <v>2.5314</v>
       </c>
       <c r="K2" t="n">
         <v>153</v>
@@ -529,7 +529,7 @@
         <v>134</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7241</v>
+        <v>6.639699999999999</v>
       </c>
       <c r="N2" t="n">
         <v>287</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0485</v>
+        <v>5.0872</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1671</v>
+        <v>1.1761</v>
       </c>
       <c r="D3" t="n">
-        <v>1.674</v>
+        <v>1.7117</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0485</v>
+        <v>5.0872</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2772</v>
+        <v>2.3664</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7713</v>
+        <v>2.7208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6193</v>
+        <v>2.4418</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4144</v>
+        <v>1.371</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7713</v>
+        <v>2.7208</v>
       </c>
       <c r="K3" t="n">
         <v>153</v>
@@ -575,7 +575,7 @@
         <v>134</v>
       </c>
       <c r="M3" t="n">
-        <v>4.185700000000001</v>
+        <v>4.0918</v>
       </c>
       <c r="N3" t="n">
         <v>287</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9945</v>
+        <v>4.955</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1546</v>
+        <v>1.1455</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6494</v>
+        <v>1.6515</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9945</v>
+        <v>4.955</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6667</v>
+        <v>2.6938</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3278</v>
+        <v>2.2612</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9041</v>
+        <v>3.6711</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1082</v>
+        <v>2.0612</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3278</v>
+        <v>2.2612</v>
       </c>
       <c r="K4" t="n">
         <v>153</v>
@@ -621,7 +621,7 @@
         <v>134</v>
       </c>
       <c r="M4" t="n">
-        <v>4.436</v>
+        <v>4.3224</v>
       </c>
       <c r="N4" t="n">
         <v>287</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1569</v>
+        <v>4.0772</v>
       </c>
       <c r="C5" t="n">
-        <v>0.961</v>
+        <v>0.9426</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2681</v>
+        <v>1.2516</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1569</v>
+        <v>4.0772</v>
       </c>
       <c r="F5" t="n">
-        <v>2.877</v>
+        <v>2.8705</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2799</v>
+        <v>1.2067</v>
       </c>
       <c r="H5" t="n">
-        <v>4.598</v>
+        <v>4.3345</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4829</v>
+        <v>2.4337</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2799</v>
+        <v>1.2067</v>
       </c>
       <c r="K5" t="n">
         <v>153</v>
@@ -667,7 +667,7 @@
         <v>134</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7628</v>
+        <v>3.6404</v>
       </c>
       <c r="N5" t="n">
         <v>287</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7603</v>
+        <v>3.7007</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8693</v>
+        <v>0.8555</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0876</v>
+        <v>1.0801</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7603</v>
+        <v>3.7007</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7367</v>
+        <v>2.7855</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0236</v>
+        <v>0.9152</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1351</v>
+        <v>4.0155</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2329</v>
+        <v>2.2546</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0236</v>
+        <v>0.9152</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -713,7 +713,7 @@
         <v>84</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2565</v>
+        <v>3.1698</v>
       </c>
       <c r="N6" t="n">
         <v>134</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2758</v>
+        <v>3.2814</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7573</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.867</v>
+        <v>0.889</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2758</v>
+        <v>3.2814</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3482</v>
+        <v>2.4368</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9276</v>
+        <v>0.8446</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8534</v>
+        <v>2.7063</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5408</v>
+        <v>1.5195</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9276</v>
+        <v>0.8446</v>
       </c>
       <c r="K7" t="n">
         <v>50</v>
@@ -759,7 +759,7 @@
         <v>84</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4684</v>
+        <v>2.3641</v>
       </c>
       <c r="N7" t="n">
         <v>134</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0758</v>
+        <v>3.0322</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7111</v>
+        <v>0.701</v>
       </c>
       <c r="D8" t="n">
-        <v>0.776</v>
+        <v>0.7755</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0758</v>
+        <v>3.0322</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3393</v>
+        <v>1.3896</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7365</v>
+        <v>1.6426</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3393</v>
+        <v>1.3896</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7232</v>
+        <v>0.7802</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7365</v>
+        <v>1.6426</v>
       </c>
       <c r="K8" t="n">
         <v>50</v>
@@ -805,7 +805,7 @@
         <v>84</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4597</v>
+        <v>2.4228</v>
       </c>
       <c r="N8" t="n">
         <v>134</v>
@@ -814,35 +814,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>znajder</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9043</v>
+        <v>2.8844</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6714</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6979</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9043</v>
+        <v>2.8844</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2358</v>
+        <v>3.0255</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6685</v>
+        <v>-0.1411</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4826</v>
+        <v>4.9164</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3406</v>
+        <v>2.7604</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6685</v>
+        <v>-0.1411</v>
       </c>
       <c r="K9" t="n">
         <v>47</v>
@@ -851,7 +851,7 @@
         <v>79</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0091</v>
+        <v>2.6193</v>
       </c>
       <c r="N9" t="n">
         <v>126</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>znajder</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8768</v>
+        <v>2.8697</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6651</v>
+        <v>0.6634</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6854</v>
+        <v>0.7015</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8768</v>
+        <v>2.8697</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0027</v>
+        <v>2.2949</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1259</v>
+        <v>0.5748</v>
       </c>
       <c r="H10" t="n">
-        <v>5.0129</v>
+        <v>2.2949</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7069</v>
+        <v>1.2885</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1259</v>
+        <v>0.5748</v>
       </c>
       <c r="K10" t="n">
         <v>47</v>
@@ -897,7 +897,7 @@
         <v>79</v>
       </c>
       <c r="M10" t="n">
-        <v>2.581</v>
+        <v>1.8633</v>
       </c>
       <c r="N10" t="n">
         <v>126</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7772</v>
+        <v>2.5328</v>
       </c>
       <c r="C11" t="n">
-        <v>0.642</v>
+        <v>0.5855</v>
       </c>
       <c r="D11" t="n">
-        <v>0.64</v>
+        <v>0.548</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7772</v>
+        <v>2.5328</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9947</v>
+        <v>1.822</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7825</v>
+        <v>0.7108</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9947</v>
+        <v>1.822</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0771</v>
+        <v>1.023</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7825</v>
+        <v>0.7108</v>
       </c>
       <c r="K11" t="n">
         <v>108</v>
@@ -943,7 +943,7 @@
         <v>139</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8596</v>
+        <v>1.7338</v>
       </c>
       <c r="N11" t="n">
         <v>247</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4769</v>
+        <v>2.4982</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5726</v>
+        <v>0.5775</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5033</v>
+        <v>0.5323</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4769</v>
+        <v>2.4982</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1844</v>
+        <v>3.1259</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7075</v>
+        <v>-0.6277</v>
       </c>
       <c r="H12" t="n">
-        <v>5.6125</v>
+        <v>5.2933</v>
       </c>
       <c r="I12" t="n">
-        <v>3.0307</v>
+        <v>2.972</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7075</v>
+        <v>-0.6277</v>
       </c>
       <c r="K12" t="n">
         <v>108</v>
@@ -989,7 +989,7 @@
         <v>139</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3232</v>
+        <v>2.3443</v>
       </c>
       <c r="N12" t="n">
         <v>247</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4119</v>
+        <v>2.4778</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5576</v>
+        <v>0.5728</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4737</v>
+        <v>0.523</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4119</v>
+        <v>2.4778</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2157</v>
+        <v>2.2176</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1962</v>
+        <v>0.2602</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4163</v>
+        <v>2.2176</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3048</v>
+        <v>1.2451</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1962</v>
+        <v>0.2602</v>
       </c>
       <c r="K13" t="n">
         <v>108</v>
@@ -1035,7 +1035,7 @@
         <v>139</v>
       </c>
       <c r="M13" t="n">
-        <v>1.501</v>
+        <v>1.5053</v>
       </c>
       <c r="N13" t="n">
         <v>247</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2653</v>
+        <v>2.2837</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5279</v>
       </c>
       <c r="D14" t="n">
-        <v>0.407</v>
+        <v>0.4345</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2653</v>
+        <v>2.2837</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2244</v>
+        <v>2.2694</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0409</v>
+        <v>0.0143</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4449</v>
+        <v>2.2694</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3202</v>
+        <v>1.2742</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0409</v>
+        <v>0.0143</v>
       </c>
       <c r="K14" t="n">
         <v>50</v>
@@ -1081,7 +1081,7 @@
         <v>84</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3611</v>
+        <v>1.2885</v>
       </c>
       <c r="N14" t="n">
         <v>134</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8617</v>
+        <v>1.9816</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4304</v>
+        <v>0.4581</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2233</v>
+        <v>0.2969</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8617</v>
+        <v>1.9816</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4317</v>
+        <v>2.5039</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.57</v>
+        <v>-0.5223</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1288</v>
+        <v>2.958</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6895</v>
+        <v>1.6608</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.57</v>
+        <v>-0.5223</v>
       </c>
       <c r="K15" t="n">
         <v>47</v>
@@ -1127,7 +1127,7 @@
         <v>79</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1195</v>
+        <v>1.1385</v>
       </c>
       <c r="N15" t="n">
         <v>126</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3208</v>
+        <v>1.2326</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3053</v>
+        <v>0.285</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0229</v>
+        <v>-0.0443</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3208</v>
+        <v>1.2326</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3208</v>
+        <v>1.2326</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3208</v>
+        <v>1.2326</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3208</v>
+        <v>1.2326</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3208</v>
+        <v>1.2326</v>
       </c>
       <c r="N16" t="n">
         <v>139</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3192</v>
+        <v>1.22</v>
       </c>
       <c r="C17" t="n">
-        <v>0.305</v>
+        <v>0.282</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0237</v>
+        <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3192</v>
+        <v>1.22</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3192</v>
+        <v>1.22</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3192</v>
+        <v>1.22</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3192</v>
+        <v>1.22</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3192</v>
+        <v>1.22</v>
       </c>
       <c r="N17" t="n">
         <v>128</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>freddieb</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1951</v>
+        <v>1.0477</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2763</v>
+        <v>0.2422</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.1285</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1951</v>
+        <v>1.0477</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1951</v>
+        <v>1.0477</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1951</v>
+        <v>1.0477</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1951</v>
+        <v>1.0477</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1951</v>
+        <v>1.0477</v>
       </c>
       <c r="N18" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>freddieb</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.149</v>
+        <v>1.0339</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2656</v>
+        <v>0.239</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1012</v>
+        <v>-0.1348</v>
       </c>
       <c r="E19" t="n">
-        <v>1.149</v>
+        <v>1.0339</v>
       </c>
       <c r="F19" t="n">
-        <v>1.149</v>
+        <v>1.0339</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.149</v>
+        <v>1.0339</v>
       </c>
       <c r="I19" t="n">
-        <v>1.149</v>
+        <v>1.0339</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.149</v>
+        <v>1.0339</v>
       </c>
       <c r="N19" t="n">
-        <v>78</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6913</v>
+        <v>0.7353</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1598</v>
+        <v>0.17</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3095</v>
+        <v>-0.2708</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6913</v>
+        <v>0.7353</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6913</v>
+        <v>1.7353</v>
       </c>
       <c r="G20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6913</v>
+        <v>1.7353</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9133</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="J20" t="n">
         <v>-1</v>
@@ -1357,7 +1357,7 @@
         <v>84</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0867</v>
+        <v>-0.02569999999999995</v>
       </c>
       <c r="N20" t="n">
         <v>134</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6846</v>
+        <v>0.6483</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1583</v>
+        <v>0.1499</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3126</v>
+        <v>-0.3105</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6846</v>
+        <v>0.6483</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6846</v>
+        <v>0.6483</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6846</v>
+        <v>0.6483</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6846</v>
+        <v>0.6483</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6846</v>
+        <v>0.6483</v>
       </c>
       <c r="N21" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6523</v>
+        <v>0.6212</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1508</v>
+        <v>0.1436</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3273</v>
+        <v>-0.3228</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6523</v>
+        <v>0.6212</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6523</v>
+        <v>0.6212</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6523</v>
+        <v>0.6212</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6523</v>
+        <v>0.6212</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6523</v>
+        <v>0.6212</v>
       </c>
       <c r="N22" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6139</v>
+        <v>0.5454</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1419</v>
+        <v>0.1261</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3447</v>
+        <v>-0.3573</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6139</v>
+        <v>0.5454</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6139</v>
+        <v>0.5454</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6139</v>
+        <v>0.5454</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6139</v>
+        <v>0.5454</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6139</v>
+        <v>0.5454</v>
       </c>
       <c r="N23" t="n">
         <v>75</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3617</v>
+        <v>0.2897</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4595</v>
+        <v>-0.4738</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3617</v>
+        <v>0.2897</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3617</v>
+        <v>0.2897</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3617</v>
+        <v>0.2897</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3617</v>
+        <v>0.2897</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3617</v>
+        <v>0.2897</v>
       </c>
       <c r="N24" t="n">
         <v>78</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2784</v>
+        <v>0.2814</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0644</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4975</v>
+        <v>-0.4776</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2784</v>
+        <v>0.2814</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2428</v>
+        <v>0.2461</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0356</v>
+        <v>0.0353</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2428</v>
+        <v>0.2461</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1311</v>
+        <v>0.1382</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0356</v>
+        <v>0.0353</v>
       </c>
       <c r="K25" t="n">
         <v>47</v>
@@ -1587,7 +1587,7 @@
         <v>79</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1667</v>
+        <v>0.1735</v>
       </c>
       <c r="N25" t="n">
         <v>126</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2454</v>
+        <v>0.2333</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0567</v>
+        <v>0.0539</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5125</v>
+        <v>-0.4995</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2454</v>
+        <v>0.2333</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4426</v>
+        <v>0.4579</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1972</v>
+        <v>-0.2246</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4426</v>
+        <v>0.4579</v>
       </c>
       <c r="I26" t="n">
-        <v>0.239</v>
+        <v>0.2571</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1972</v>
+        <v>-0.2246</v>
       </c>
       <c r="K26" t="n">
         <v>47</v>
@@ -1633,7 +1633,7 @@
         <v>79</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0418</v>
+        <v>0.0325</v>
       </c>
       <c r="N26" t="n">
         <v>126</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0076</v>
+        <v>0.0974</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0018</v>
+        <v>0.0225</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6277</v>
+        <v>-0.5614</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0076</v>
+        <v>0.0974</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0076</v>
+        <v>-1.9593</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.0567</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0076</v>
+        <v>-1.9593</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0076</v>
+        <v>-1.1001</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2.0567</v>
       </c>
       <c r="K27" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0076</v>
+        <v>0.9566000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>128</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0713</v>
+        <v>-0.0905</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0165</v>
+        <v>-0.0209</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6567</v>
+        <v>-0.647</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0713</v>
+        <v>-0.0905</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0713</v>
+        <v>-0.0905</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0713</v>
+        <v>-0.0905</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0713</v>
+        <v>-0.0905</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0713</v>
+        <v>-0.0905</v>
       </c>
       <c r="N28" t="n">
         <v>78</v>
@@ -1734,47 +1734,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1018</v>
+        <v>-0.1277</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0235</v>
+        <v>-0.0295</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6705</v>
+        <v>-0.664</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1018</v>
+        <v>-0.1277</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.2221</v>
+        <v>-0.1277</v>
       </c>
       <c r="G29" t="n">
-        <v>2.1203</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.2221</v>
+        <v>-0.1277</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.1999</v>
+        <v>-0.1277</v>
       </c>
       <c r="J29" t="n">
-        <v>2.1203</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="L29" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9203999999999999</v>
+        <v>-0.1277</v>
       </c>
       <c r="N29" t="n">
-        <v>287</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1924</v>
+        <v>-0.1969</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0445</v>
+        <v>-0.0455</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7118</v>
+        <v>-0.6955</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1924</v>
+        <v>-0.1969</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1924</v>
+        <v>-0.1969</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1924</v>
+        <v>-0.1969</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1924</v>
+        <v>-0.1969</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1924</v>
+        <v>-0.1969</v>
       </c>
       <c r="N30" t="n">
         <v>139</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2015</v>
+        <v>-0.212</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0466</v>
+        <v>-0.049</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7159</v>
+        <v>-0.7024</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2015</v>
+        <v>-0.212</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2015</v>
+        <v>-0.212</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2015</v>
+        <v>-0.212</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2015</v>
+        <v>-0.212</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2015</v>
+        <v>-0.212</v>
       </c>
       <c r="N31" t="n">
         <v>128</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2237</v>
+        <v>-0.2192</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0517</v>
+        <v>-0.0507</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.726</v>
+        <v>-0.7056</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2237</v>
+        <v>-0.2192</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2237</v>
+        <v>-0.2192</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2237</v>
+        <v>-0.2192</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2237</v>
+        <v>-0.2192</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2237</v>
+        <v>-0.2192</v>
       </c>
       <c r="N32" t="n">
         <v>128</v>
@@ -1918,139 +1918,139 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.429</v>
+        <v>-0.3839</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0992</v>
+        <v>-0.0888</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8195</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.429</v>
+        <v>-0.3839</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.429</v>
+        <v>-0.3839</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.429</v>
+        <v>-0.3839</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.429</v>
+        <v>-0.3839</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.429</v>
+        <v>-0.3839</v>
       </c>
       <c r="N33" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4353</v>
+        <v>-0.3872</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1006</v>
+        <v>-0.0895</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8224</v>
+        <v>-0.7822</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4353</v>
+        <v>-0.3872</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4353</v>
+        <v>-0.1208</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.2664</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4353</v>
+        <v>-0.1208</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4353</v>
+        <v>-0.0678</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.2664</v>
       </c>
       <c r="K34" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4353</v>
+        <v>-0.3342000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>78</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4976</v>
+        <v>-0.4002</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.115</v>
+        <v>-0.0925</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8507</v>
+        <v>-0.7881</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4976</v>
+        <v>-0.4002</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2406</v>
+        <v>-0.4002</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.257</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2406</v>
+        <v>-0.4002</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1299</v>
+        <v>-0.4002</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.257</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="L35" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3869</v>
+        <v>-0.4002</v>
       </c>
       <c r="N35" t="n">
-        <v>247</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7389</v>
+        <v>-0.6853</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1708</v>
+        <v>-0.1584</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9606</v>
+        <v>-0.918</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7389</v>
+        <v>-0.6853</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7389</v>
+        <v>-0.6853</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7389</v>
+        <v>-0.6853</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7389</v>
+        <v>-0.6853</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7389</v>
+        <v>-0.6853</v>
       </c>
       <c r="N36" t="n">
         <v>75</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7784</v>
+        <v>-0.7431</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.18</v>
+        <v>-0.1718</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9785</v>
+        <v>-0.9443</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7784</v>
+        <v>-0.7431</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7784</v>
+        <v>-0.7431</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7784</v>
+        <v>-0.7431</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7784</v>
+        <v>-0.7431</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7784</v>
+        <v>-0.7431</v>
       </c>
       <c r="N37" t="n">
         <v>75</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8337</v>
+        <v>-0.7976</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1927</v>
+        <v>-0.1844</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0037</v>
+        <v>-0.9691</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8337</v>
+        <v>-0.7976</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8337</v>
+        <v>-0.7976</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8337</v>
+        <v>-0.7976</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8337</v>
+        <v>-0.7976</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8337</v>
+        <v>-0.7976</v>
       </c>
       <c r="N38" t="n">
         <v>75</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9349</v>
+        <v>-0.8941</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2161</v>
+        <v>-0.2067</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0498</v>
+        <v>-1.0131</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9349</v>
+        <v>-0.8941</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9349</v>
+        <v>-0.8941</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9349</v>
+        <v>-0.8941</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9349</v>
+        <v>-0.8941</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9349</v>
+        <v>-0.8941</v>
       </c>
       <c r="N39" t="n">
         <v>78</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.0479</v>
+        <v>-0.9372</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2423</v>
+        <v>-0.2167</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1012</v>
+        <v>-1.0327</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.0479</v>
+        <v>-0.9372</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.0479</v>
+        <v>-0.9372</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.0479</v>
+        <v>-0.9372</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.0479</v>
+        <v>-0.9372</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.0479</v>
+        <v>-0.9372</v>
       </c>
       <c r="N40" t="n">
         <v>139</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8959</v>
+        <v>-1.598</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4383</v>
+        <v>-0.3694</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4873</v>
+        <v>-1.3338</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8959</v>
+        <v>-1.598</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.1178</v>
+        <v>-1.8206</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2219</v>
+        <v>0.2226</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.1178</v>
+        <v>-1.8206</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.1436</v>
+        <v>-1.0222</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2219</v>
+        <v>0.2226</v>
       </c>
       <c r="K41" t="n">
         <v>108</v>
@@ -2323,7 +2323,7 @@
         <v>139</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.9217</v>
+        <v>-0.7996</v>
       </c>
       <c r="N41" t="n">
         <v>247</v>
@@ -2429,10 +2429,10 @@
         <v>1.65</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3957</v>
+        <v>1.4313</v>
       </c>
       <c r="J2" t="n">
-        <v>36.2882</v>
+        <v>37.2138</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.25</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6446</v>
+        <v>0.6153</v>
       </c>
       <c r="J3" t="n">
-        <v>16.7596</v>
+        <v>15.9978</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6039</v>
+        <v>0.5734</v>
       </c>
       <c r="J4" t="n">
-        <v>15.7014</v>
+        <v>14.9084</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3024</v>
+        <v>0.2705</v>
       </c>
       <c r="J5" t="n">
-        <v>7.8624</v>
+        <v>7.033</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
       <c r="J6" t="n">
-        <v>0.468</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1794</v>
+        <v>0.142</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6644</v>
+        <v>3.692</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0256</v>
+        <v>0.02</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6656</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2288</v>
+        <v>-0.2098</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.9488</v>
+        <v>-5.4548</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.71</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3242</v>
+        <v>-0.3075</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.4292</v>
+        <v>-7.995</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3334</v>
+        <v>-0.3172</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.6684</v>
+        <v>-8.247199999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9778</v>
+        <v>0.9686</v>
       </c>
       <c r="J12" t="n">
-        <v>28.3562</v>
+        <v>28.0894</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8044</v>
+        <v>0.7822</v>
       </c>
       <c r="J13" t="n">
-        <v>23.3276</v>
+        <v>22.6838</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.22</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5831</v>
+        <v>0.5521</v>
       </c>
       <c r="J14" t="n">
-        <v>16.9099</v>
+        <v>16.0109</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4502</v>
+        <v>0.4172</v>
       </c>
       <c r="J15" t="n">
-        <v>13.0558</v>
+        <v>12.0988</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3027</v>
+        <v>0.2708</v>
       </c>
       <c r="J16" t="n">
-        <v>8.7783</v>
+        <v>7.8532</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.11</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3103</v>
+        <v>0.2618</v>
       </c>
       <c r="J17" t="n">
-        <v>8.998699999999999</v>
+        <v>7.5922</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.88</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1577</v>
+        <v>-0.1407</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.5733</v>
+        <v>-4.0803</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1987</v>
+        <v>-0.1803</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.7623</v>
+        <v>-5.2287</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.74</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2957</v>
+        <v>-0.2778</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.5753</v>
+        <v>-8.0562</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.68</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3514</v>
+        <v>-0.3362</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.1906</v>
+        <v>-9.7498</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.35</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6197</v>
+        <v>0.5917</v>
       </c>
       <c r="J22" t="n">
-        <v>17.3516</v>
+        <v>16.5676</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3878</v>
+        <v>0.3321</v>
       </c>
       <c r="J23" t="n">
-        <v>10.8584</v>
+        <v>9.2988</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0464</v>
+        <v>0.031</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2992</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.71</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3361</v>
+        <v>-0.3203</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.4108</v>
+        <v>-8.968400000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.63</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4086</v>
+        <v>-0.399</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.4408</v>
+        <v>-11.172</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.35</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7542</v>
+        <v>0.7383</v>
       </c>
       <c r="J27" t="n">
-        <v>21.1176</v>
+        <v>20.6724</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.25</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6021</v>
+        <v>0.5906</v>
       </c>
       <c r="J28" t="n">
-        <v>16.8588</v>
+        <v>16.5368</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5546</v>
+        <v>0.5453</v>
       </c>
       <c r="J29" t="n">
-        <v>15.5288</v>
+        <v>15.2684</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.97</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1622</v>
+        <v>-0.1306</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.5416</v>
+        <v>-3.6568</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.95</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2279</v>
+        <v>-0.1909</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.3812</v>
+        <v>-5.3452</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.57</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6172</v>
+        <v>0.5785</v>
       </c>
       <c r="J32" t="n">
-        <v>16.0472</v>
+        <v>15.041</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.53</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5522</v>
       </c>
       <c r="J33" t="n">
-        <v>15.2932</v>
+        <v>14.3572</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.5</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5662</v>
+        <v>0.5313</v>
       </c>
       <c r="J34" t="n">
-        <v>14.7212</v>
+        <v>13.8138</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.98</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0535</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.6952</v>
+        <v>-1.391</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.92</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1471</v>
+        <v>-0.1292</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.8246</v>
+        <v>-3.3592</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.96</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0509</v>
+        <v>-0.0401</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.3234</v>
+        <v>-1.0426</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.85</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1839</v>
+        <v>-0.1675</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.7814</v>
+        <v>-4.355</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.77</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2619</v>
+        <v>-0.2445</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.8094</v>
+        <v>-6.357</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.77</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2619</v>
+        <v>-0.2445</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.8094</v>
+        <v>-6.357</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.62</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3994</v>
+        <v>-0.3878</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.3844</v>
+        <v>-10.0828</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5286</v>
+        <v>0.4987</v>
       </c>
       <c r="J42" t="n">
-        <v>15.858</v>
+        <v>14.961</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.21</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4422</v>
+        <v>0.3881</v>
       </c>
       <c r="J43" t="n">
-        <v>13.266</v>
+        <v>11.643</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.16</v>
       </c>
       <c r="I44" t="n">
-        <v>0.36</v>
+        <v>0.3057</v>
       </c>
       <c r="J44" t="n">
-        <v>10.8</v>
+        <v>9.170999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0264</v>
+        <v>-0.0188</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.792</v>
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.46</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5577</v>
+        <v>-0.5683</v>
       </c>
       <c r="J46" t="n">
-        <v>-16.731</v>
+        <v>-17.049</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.4</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8368</v>
+        <v>0.821</v>
       </c>
       <c r="J47" t="n">
-        <v>25.104</v>
+        <v>24.63</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.11</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3486</v>
+        <v>0.311</v>
       </c>
       <c r="J48" t="n">
-        <v>10.458</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.08</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2715</v>
+        <v>0.2371</v>
       </c>
       <c r="J49" t="n">
-        <v>8.145</v>
+        <v>7.113</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1539</v>
+        <v>0.1282</v>
       </c>
       <c r="J50" t="n">
-        <v>4.617</v>
+        <v>3.846</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.9</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3629</v>
+        <v>-0.3204</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.887</v>
+        <v>-9.612</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3705</v>
+        <v>0.3196</v>
       </c>
       <c r="J52" t="n">
-        <v>10.0035</v>
+        <v>8.629200000000001</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1115</v>
+        <v>-0.0968</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.0105</v>
+        <v>-2.6136</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.8</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2378</v>
+        <v>-0.219</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.4206</v>
+        <v>-5.913</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3418</v>
+        <v>-0.3261</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.2286</v>
+        <v>-8.8047</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.351</v>
+        <v>-0.3358</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.477</v>
+        <v>-9.066599999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.53</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9761</v>
+        <v>0.9636</v>
       </c>
       <c r="J57" t="n">
-        <v>26.3547</v>
+        <v>26.0172</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.35</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7304</v>
+        <v>0.7191</v>
       </c>
       <c r="J58" t="n">
-        <v>19.7208</v>
+        <v>19.4157</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.24</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5703</v>
+        <v>0.5659</v>
       </c>
       <c r="J59" t="n">
-        <v>15.3981</v>
+        <v>15.2793</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.23</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5547</v>
+        <v>0.5511</v>
       </c>
       <c r="J60" t="n">
-        <v>14.9769</v>
+        <v>14.8797</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.21</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5229</v>
+        <v>0.5181</v>
       </c>
       <c r="J61" t="n">
-        <v>14.1183</v>
+        <v>13.9887</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.6</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6381</v>
+        <v>0.5975</v>
       </c>
       <c r="J62" t="n">
-        <v>17.8668</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.48</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>15.4252</v>
+        <v>14.4368</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.29</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3945</v>
+        <v>0.3357</v>
       </c>
       <c r="J64" t="n">
-        <v>11.046</v>
+        <v>9.3996</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.23</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3273</v>
+        <v>0.2743</v>
       </c>
       <c r="J65" t="n">
-        <v>9.164400000000001</v>
+        <v>7.6804</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1353</v>
+        <v>-0.1179</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.7884</v>
+        <v>-3.3012</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2304</v>
+        <v>0.2213</v>
       </c>
       <c r="J67" t="n">
-        <v>6.4512</v>
+        <v>6.1964</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.86</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1718</v>
+        <v>-0.1558</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.8104</v>
+        <v>-4.3624</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.72</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3072</v>
+        <v>-0.2907</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.601599999999999</v>
+        <v>-8.1396</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.63</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3891</v>
+        <v>-0.3767</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.8948</v>
+        <v>-10.5476</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.61</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.407</v>
+        <v>-0.396</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.396</v>
+        <v>-11.088</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.97</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.0293</v>
+        <v>-0.0191</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.7032</v>
+        <v>-0.4584</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.79</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2407</v>
+        <v>-0.2245</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.7768</v>
+        <v>-5.388</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.75</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2775</v>
+        <v>-0.2613</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.66</v>
+        <v>-6.2712</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3232</v>
+        <v>-0.3076</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.7568</v>
+        <v>-7.3824</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.59</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4222</v>
+        <v>-0.4125</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.1328</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9325</v>
+        <v>0.9184</v>
       </c>
       <c r="J77" t="n">
-        <v>22.38</v>
+        <v>22.0416</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.48</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.9046</v>
       </c>
       <c r="J78" t="n">
-        <v>22.0536</v>
+        <v>21.7104</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5448</v>
+        <v>0.5396</v>
       </c>
       <c r="J79" t="n">
-        <v>13.0752</v>
+        <v>12.9504</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.06</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1906</v>
+        <v>0.1628</v>
       </c>
       <c r="J80" t="n">
-        <v>4.5744</v>
+        <v>3.9072</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.02</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0584</v>
+        <v>0.0421</v>
       </c>
       <c r="J81" t="n">
-        <v>1.4016</v>
+        <v>1.0104</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.45</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0488</v>
+        <v>1.0543</v>
       </c>
       <c r="J82" t="n">
-        <v>30.4152</v>
+        <v>30.5747</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.38</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.914</v>
       </c>
       <c r="J83" t="n">
-        <v>26.9381</v>
+        <v>26.506</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.03</v>
       </c>
       <c r="I84" t="n">
-        <v>0.116</v>
+        <v>0.0946</v>
       </c>
       <c r="J84" t="n">
-        <v>3.364</v>
+        <v>2.7434</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.98</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1226</v>
+        <v>-0.0955</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.5554</v>
+        <v>-2.7695</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5669</v>
+        <v>-0.5284</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.4401</v>
+        <v>-15.3236</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.13</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3129</v>
+        <v>0.2613</v>
       </c>
       <c r="J87" t="n">
-        <v>9.0741</v>
+        <v>7.5777</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.01</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0451</v>
+        <v>0.0302</v>
       </c>
       <c r="J88" t="n">
-        <v>1.3079</v>
+        <v>0.8758</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0572</v>
+        <v>-0.0451</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.6588</v>
+        <v>-1.3079</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0849</v>
+        <v>-0.0696</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.4621</v>
+        <v>-2.0184</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1895</v>
+        <v>-0.169</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.4955</v>
+        <v>-4.901</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.27</v>
       </c>
       <c r="I92" t="n">
-        <v>0.716</v>
+        <v>0.6836</v>
       </c>
       <c r="J92" t="n">
-        <v>21.48</v>
+        <v>20.508</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6297</v>
+        <v>0.5929</v>
       </c>
       <c r="J93" t="n">
-        <v>18.891</v>
+        <v>17.787</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3753</v>
+        <v>0.336</v>
       </c>
       <c r="J94" t="n">
-        <v>11.259</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.97</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1515</v>
+        <v>-0.1204</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.545</v>
+        <v>-3.612</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.86</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4624</v>
+        <v>-0.42</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.872</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.31</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6087</v>
+        <v>0.5496</v>
       </c>
       <c r="J97" t="n">
-        <v>18.261</v>
+        <v>16.488</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2099</v>
+        <v>0.1681</v>
       </c>
       <c r="J98" t="n">
-        <v>6.297</v>
+        <v>5.043</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0007</v>
+        <v>-0.0003</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.021</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.86</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1923</v>
+        <v>-0.1717</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.769</v>
+        <v>-5.151</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.83</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2236</v>
+        <v>-0.2031</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.708</v>
+        <v>-6.093</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.78</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8793</v>
+        <v>0.8099</v>
       </c>
       <c r="J102" t="n">
-        <v>19.3446</v>
+        <v>17.8178</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.44</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5506</v>
+        <v>0.4819</v>
       </c>
       <c r="J103" t="n">
-        <v>12.1132</v>
+        <v>10.6018</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.33</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4368</v>
+        <v>0.3747</v>
       </c>
       <c r="J104" t="n">
-        <v>9.6096</v>
+        <v>8.243399999999999</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.13</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2028</v>
+        <v>0.1629</v>
       </c>
       <c r="J105" t="n">
-        <v>4.4616</v>
+        <v>3.5838</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2457</v>
+        <v>-0.2282</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.4054</v>
+        <v>-5.0204</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.02</v>
       </c>
       <c r="I107" t="n">
-        <v>0.0788</v>
+        <v>0.0659</v>
       </c>
       <c r="J107" t="n">
-        <v>1.7336</v>
+        <v>1.4498</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.97</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0459</v>
+        <v>-0.0366</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.0098</v>
+        <v>-0.8052</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1793</v>
+        <v>-0.1612</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.9446</v>
+        <v>-3.5464</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.84</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1993</v>
+        <v>-0.1806</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.3846</v>
+        <v>-3.9732</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.6</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4242</v>
+        <v>-0.4151</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.3324</v>
+        <v>-9.132199999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.15</v>
       </c>
       <c r="I112" t="n">
-        <v>0.391</v>
+        <v>0.3398</v>
       </c>
       <c r="J112" t="n">
-        <v>9.775</v>
+        <v>8.494999999999999</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.9</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1346</v>
+        <v>-0.1188</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.365</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.76</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.276</v>
+        <v>-0.2576</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.9</v>
+        <v>-6.44</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2949</v>
+        <v>-0.277</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.3725</v>
+        <v>-6.925</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.66</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3687</v>
+        <v>-0.3548</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.217499999999999</v>
+        <v>-8.869999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.73</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3941</v>
+        <v>1.4195</v>
       </c>
       <c r="J117" t="n">
-        <v>34.8525</v>
+        <v>35.4875</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.55</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1595</v>
+        <v>1.1729</v>
       </c>
       <c r="J118" t="n">
-        <v>28.9875</v>
+        <v>29.3225</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.29</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.6976</v>
       </c>
       <c r="J119" t="n">
-        <v>18.0825</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2781</v>
+        <v>-0.241</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.9525</v>
+        <v>-6.025</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.6277</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.445</v>
+        <v>-15.6925</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.08</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2462</v>
+        <v>0.2019</v>
       </c>
       <c r="J122" t="n">
-        <v>5.9088</v>
+        <v>4.8456</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.95</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0743</v>
+        <v>-0.0622</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.7832</v>
+        <v>-1.4928</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.82</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2191</v>
+        <v>-0.2001</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.2584</v>
+        <v>-4.8024</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2289</v>
+        <v>-0.2099</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.4936</v>
+        <v>-5.0376</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.62</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4062</v>
+        <v>-0.3954</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.748799999999999</v>
+        <v>-9.489599999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.42</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9938</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>23.8512</v>
+        <v>23.7456</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6362</v>
+        <v>0.6021</v>
       </c>
       <c r="J128" t="n">
-        <v>15.2688</v>
+        <v>14.4504</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.17</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4835</v>
+        <v>0.4468</v>
       </c>
       <c r="J129" t="n">
-        <v>11.604</v>
+        <v>10.7232</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.14</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4154</v>
+        <v>0.379</v>
       </c>
       <c r="J130" t="n">
-        <v>9.9696</v>
+        <v>9.096</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.83</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5484</v>
+        <v>-0.5097</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.1616</v>
+        <v>-12.2328</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.42</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9974</v>
+        <v>0.9936</v>
       </c>
       <c r="J132" t="n">
-        <v>25.9324</v>
+        <v>25.8336</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.21</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5376</v>
       </c>
       <c r="J133" t="n">
-        <v>14.9266</v>
+        <v>13.9776</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4169</v>
+        <v>0.3798</v>
       </c>
       <c r="J134" t="n">
-        <v>10.8394</v>
+        <v>9.8748</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.14</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4169</v>
+        <v>0.3798</v>
       </c>
       <c r="J135" t="n">
-        <v>10.8394</v>
+        <v>9.8748</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.82</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5695</v>
+        <v>-0.5314</v>
       </c>
       <c r="J136" t="n">
-        <v>-14.807</v>
+        <v>-13.8164</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.35</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6953</v>
+        <v>0.6418</v>
       </c>
       <c r="J137" t="n">
-        <v>18.0778</v>
+        <v>16.6868</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.095</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.47</v>
+        <v>-2.0722</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1531</v>
+        <v>-0.134</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.9806</v>
+        <v>-3.484</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1749</v>
+        <v>-0.155</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.5474</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.65</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3876</v>
+        <v>-0.3757</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.0776</v>
+        <v>-9.7682</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.26</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.6794</v>
       </c>
       <c r="J142" t="n">
-        <v>20.6538</v>
+        <v>19.7026</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.03</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1315</v>
+        <v>0.1055</v>
       </c>
       <c r="J143" t="n">
-        <v>3.8135</v>
+        <v>3.0595</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0038</v>
+        <v>-0.002</v>
       </c>
       <c r="J144" t="n">
-        <v>-0.1102</v>
+        <v>-0.058</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.97</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1405</v>
+        <v>-0.1112</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.0745</v>
+        <v>-3.2248</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.89</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3743</v>
+        <v>-0.3314</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.8547</v>
+        <v>-9.6106</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.39</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7195</v>
+        <v>0.6623</v>
       </c>
       <c r="J147" t="n">
-        <v>20.8655</v>
+        <v>19.2067</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.14</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3179</v>
+        <v>0.267</v>
       </c>
       <c r="J148" t="n">
-        <v>9.219099999999999</v>
+        <v>7.743</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.142</v>
+        <v>0.1107</v>
       </c>
       <c r="J149" t="n">
-        <v>4.118</v>
+        <v>3.2103</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.97</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0624</v>
+        <v>-0.0488</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.8096</v>
+        <v>-1.4152</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.73</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3247</v>
+        <v>-0.3087</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.4163</v>
+        <v>-8.952299999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.32</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.5758</v>
       </c>
       <c r="J152" t="n">
-        <v>19.008</v>
+        <v>17.274</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.97</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0572</v>
+        <v>-0.0451</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.716</v>
+        <v>-1.353</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.93</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1102</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.306</v>
+        <v>-2.784</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.87</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1788</v>
+        <v>-0.1584</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.364</v>
+        <v>-4.752</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.83</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2207</v>
+        <v>-0.2002</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.621</v>
+        <v>-6.006</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.35</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8546</v>
+        <v>0.8337</v>
       </c>
       <c r="J157" t="n">
-        <v>25.638</v>
+        <v>25.011</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.32</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7699</v>
       </c>
       <c r="J158" t="n">
-        <v>23.847</v>
+        <v>23.097</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.2</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5458</v>
+        <v>0.5113</v>
       </c>
       <c r="J159" t="n">
-        <v>16.374</v>
+        <v>15.339</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.18</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5028</v>
+        <v>0.4678</v>
       </c>
       <c r="J160" t="n">
-        <v>15.084</v>
+        <v>14.034</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.91</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3518</v>
+        <v>-0.3108</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.554</v>
+        <v>-9.324</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.99</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.012</v>
+        <v>-0.0077</v>
       </c>
       <c r="J162" t="n">
-        <v>-0.276</v>
+        <v>-0.1771</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.9</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1364</v>
+        <v>-0.1202</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.1372</v>
+        <v>-2.7646</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.88</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1585</v>
+        <v>-0.1412</v>
       </c>
       <c r="J164" t="n">
-        <v>-3.6455</v>
+        <v>-3.2476</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2682</v>
+        <v>-0.2494</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.1686</v>
+        <v>-5.7362</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.76</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2778</v>
+        <v>-0.2592</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.3894</v>
+        <v>-5.9616</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.55</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1603</v>
+        <v>1.1737</v>
       </c>
       <c r="J167" t="n">
-        <v>26.6869</v>
+        <v>26.9951</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.55</v>
       </c>
       <c r="I168" t="n">
-        <v>1.1603</v>
+        <v>1.1737</v>
       </c>
       <c r="J168" t="n">
-        <v>26.6869</v>
+        <v>26.9951</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.13</v>
       </c>
       <c r="I169" t="n">
-        <v>0.377</v>
+        <v>0.3443</v>
       </c>
       <c r="J169" t="n">
-        <v>8.670999999999999</v>
+        <v>7.9189</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.08</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2473</v>
+        <v>0.2171</v>
       </c>
       <c r="J170" t="n">
-        <v>5.6879</v>
+        <v>4.9933</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1812</v>
+        <v>-0.1506</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.1676</v>
+        <v>-3.4638</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.07</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2569</v>
+        <v>0.2185</v>
       </c>
       <c r="J172" t="n">
-        <v>6.1656</v>
+        <v>5.244</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.85</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1803</v>
+        <v>-0.1644</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.3272</v>
+        <v>-3.9456</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2872</v>
+        <v>-0.2708</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.8928</v>
+        <v>-6.4992</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.65</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3692</v>
+        <v>-0.3556</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.860799999999999</v>
+        <v>-8.5344</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.52</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4845</v>
+        <v>-0.4813</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.628</v>
+        <v>-11.5512</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.55</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1469</v>
+        <v>1.1607</v>
       </c>
       <c r="J177" t="n">
-        <v>27.5256</v>
+        <v>27.8568</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.36</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8498</v>
+        <v>0.8346</v>
       </c>
       <c r="J178" t="n">
-        <v>20.3952</v>
+        <v>20.0304</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.29</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7164</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>17.1936</v>
+        <v>16.6584</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7164</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>17.1936</v>
+        <v>16.6584</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.16</v>
       </c>
       <c r="I181" t="n">
-        <v>0.4372</v>
+        <v>0.4059</v>
       </c>
       <c r="J181" t="n">
-        <v>10.4928</v>
+        <v>9.7416</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.6</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2371</v>
+        <v>1.2539</v>
       </c>
       <c r="J182" t="n">
-        <v>34.6388</v>
+        <v>35.1092</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.48</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0744</v>
+        <v>1.0832</v>
       </c>
       <c r="J183" t="n">
-        <v>30.0832</v>
+        <v>30.3296</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.18</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5008</v>
+        <v>0.4667</v>
       </c>
       <c r="J184" t="n">
-        <v>14.0224</v>
+        <v>13.0676</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3819</v>
+        <v>-0.3411</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.6932</v>
+        <v>-9.550800000000001</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.89</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4082</v>
+        <v>-0.3674</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.4296</v>
+        <v>-10.2872</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.08</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2268</v>
+        <v>0.1825</v>
       </c>
       <c r="J187" t="n">
-        <v>6.3504</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.98</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.038</v>
+        <v>-0.0297</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.064</v>
+        <v>-0.8316</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.98</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.038</v>
+        <v>-0.0297</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.064</v>
+        <v>-0.8316</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.92</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1182</v>
+        <v>-0.1014</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.3096</v>
+        <v>-2.8392</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3593</v>
+        <v>-0.3449</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.0604</v>
+        <v>-9.6572</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.27</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6073</v>
+        <v>0.5586</v>
       </c>
       <c r="J192" t="n">
-        <v>13.9679</v>
+        <v>12.8478</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.84</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.198</v>
+        <v>-0.1801</v>
       </c>
       <c r="J193" t="n">
-        <v>-4.554</v>
+        <v>-4.1423</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.77</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2658</v>
+        <v>-0.2474</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.1134</v>
+        <v>-5.6902</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.74</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2942</v>
+        <v>-0.2765</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.7666</v>
+        <v>-6.3595</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4571</v>
+        <v>-0.4514</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.5133</v>
+        <v>-10.3822</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.86</v>
       </c>
       <c r="I197" t="n">
-        <v>1.56</v>
+        <v>1.5997</v>
       </c>
       <c r="J197" t="n">
-        <v>35.88</v>
+        <v>36.7931</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.42</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9731</v>
+        <v>0.9667</v>
       </c>
       <c r="J198" t="n">
-        <v>22.3813</v>
+        <v>22.2341</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.24</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6242</v>
+        <v>0.5944</v>
       </c>
       <c r="J199" t="n">
-        <v>14.3566</v>
+        <v>13.6712</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.93</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3061</v>
+        <v>-0.2677</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.0403</v>
+        <v>-6.1571</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6108</v>
+        <v>-0.5775</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.0484</v>
+        <v>-13.2825</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.32</v>
       </c>
       <c r="I202" t="n">
-        <v>0.633</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="J202" t="n">
-        <v>18.357</v>
+        <v>16.6779</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.05</v>
       </c>
       <c r="I203" t="n">
-        <v>0.15</v>
+        <v>0.1153</v>
       </c>
       <c r="J203" t="n">
-        <v>4.35</v>
+        <v>3.3437</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.04</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1266</v>
+        <v>0.0955</v>
       </c>
       <c r="J204" t="n">
-        <v>3.6714</v>
+        <v>2.7695</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2708</v>
+        <v>-0.2515</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.8532</v>
+        <v>-7.2935</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.74</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3091</v>
+        <v>-0.2917</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.963900000000001</v>
+        <v>-8.459300000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.36</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8955</v>
+        <v>0.8769</v>
       </c>
       <c r="J207" t="n">
-        <v>25.9695</v>
+        <v>25.4301</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.32</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8143</v>
+        <v>0.7889</v>
       </c>
       <c r="J208" t="n">
-        <v>23.6147</v>
+        <v>22.8781</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.11</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3482</v>
+        <v>0.3109</v>
       </c>
       <c r="J209" t="n">
-        <v>10.0978</v>
+        <v>9.0161</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.02</v>
       </c>
       <c r="I210" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="J210" t="n">
-        <v>2.4099</v>
+        <v>1.9053</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.75</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.6929</v>
       </c>
       <c r="J211" t="n">
-        <v>-20.9467</v>
+        <v>-20.0941</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.5</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0953</v>
+        <v>1.1063</v>
       </c>
       <c r="J212" t="n">
-        <v>27.3825</v>
+        <v>27.6575</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.41</v>
       </c>
       <c r="I213" t="n">
-        <v>0.9573</v>
+        <v>0.9482</v>
       </c>
       <c r="J213" t="n">
-        <v>23.9325</v>
+        <v>23.705</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.34</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8243</v>
+        <v>0.8033</v>
       </c>
       <c r="J214" t="n">
-        <v>20.6075</v>
+        <v>20.0825</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.02</v>
       </c>
       <c r="I215" t="n">
-        <v>0.0601</v>
+        <v>0.0438</v>
       </c>
       <c r="J215" t="n">
-        <v>1.5025</v>
+        <v>1.095</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.95</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2449</v>
+        <v>-0.209</v>
       </c>
       <c r="J216" t="n">
-        <v>-6.1225</v>
+        <v>-5.225</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.19</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4689</v>
+        <v>0.4176</v>
       </c>
       <c r="J217" t="n">
-        <v>11.7225</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.96</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0571</v>
+        <v>-0.0464</v>
       </c>
       <c r="J218" t="n">
-        <v>-1.4275</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.76</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2749</v>
+        <v>-0.2567</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.8725</v>
+        <v>-6.4175</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.64</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3857</v>
+        <v>-0.373</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.6425</v>
+        <v>-9.324999999999999</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.61</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4126</v>
+        <v>-0.4022</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.315</v>
+        <v>-10.055</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2952</v>
+        <v>1.3154</v>
       </c>
       <c r="J222" t="n">
-        <v>28.4944</v>
+        <v>28.9388</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.55</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1314</v>
+        <v>1.1476</v>
       </c>
       <c r="J223" t="n">
-        <v>24.8908</v>
+        <v>25.2472</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.45</v>
       </c>
       <c r="I224" t="n">
-        <v>0.9958</v>
+        <v>1.0007</v>
       </c>
       <c r="J224" t="n">
-        <v>21.9076</v>
+        <v>22.0154</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.35</v>
       </c>
       <c r="I225" t="n">
-        <v>0.8194</v>
+        <v>0.8075</v>
       </c>
       <c r="J225" t="n">
-        <v>18.0268</v>
+        <v>17.765</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.18</v>
       </c>
       <c r="I226" t="n">
-        <v>0.4664</v>
+        <v>0.4363</v>
       </c>
       <c r="J226" t="n">
-        <v>10.2608</v>
+        <v>9.598599999999999</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.05</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2485</v>
+        <v>0.2228</v>
       </c>
       <c r="J227" t="n">
-        <v>5.467</v>
+        <v>4.9016</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.78</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2404</v>
+        <v>-0.2259</v>
       </c>
       <c r="J228" t="n">
-        <v>-5.2888</v>
+        <v>-4.9698</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.65</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3598</v>
+        <v>-0.3474</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.9156</v>
+        <v>-7.6428</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.48</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5097</v>
+        <v>-0.5091</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.2134</v>
+        <v>-11.2002</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.47</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5185</v>
+        <v>-0.519</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.407</v>
+        <v>-11.418</v>
       </c>
     </row>
   </sheetData>
